--- a/research/traditional_assets/database/data/ireland/ireland_business_consumer_services.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_business_consumer_services.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09471852104142724</v>
+        <v>0.09463949789012546</v>
       </c>
       <c r="C2">
-        <v>44518.65358566186</v>
+        <v>44143.62812200282</v>
       </c>
       <c r="D2">
-        <v>44273.65358566186</v>
+        <v>44345.28912200282</v>
       </c>
       <c r="E2">
-        <v>-5198</v>
+        <v>-4751.339</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>446.661</v>
       </c>
       <c r="G2">
         <v>245</v>
@@ -1457,28 +1457,28 @@
         <v>1490</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>22.4670483</v>
       </c>
       <c r="N2">
-        <v>1490</v>
+        <v>1467.5329517</v>
       </c>
       <c r="O2">
-        <v>186.25</v>
+        <v>183.4416189625</v>
       </c>
       <c r="P2">
-        <v>1303.75</v>
+        <v>1284.0913327375</v>
       </c>
       <c r="Q2">
-        <v>2017.75</v>
+        <v>1998.0913327375</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09471852104142724</v>
+        <v>0.09515088170719743</v>
       </c>
       <c r="T2">
-        <v>0.9535130270927494</v>
+        <v>0.9619405412210945</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>66.31934823409803</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09463949789012546</v>
+        <v>0.09456047473882367</v>
       </c>
       <c r="C3">
-        <v>44143.62812200282</v>
+        <v>43768.83484910309</v>
       </c>
       <c r="D3">
-        <v>44345.28912200282</v>
+        <v>44417.15684910309</v>
       </c>
       <c r="E3">
-        <v>-4751.339</v>
+        <v>-4304.678</v>
       </c>
       <c r="F3">
-        <v>446.661</v>
+        <v>893.322</v>
       </c>
       <c r="G3">
         <v>245</v>
@@ -1539,28 +1539,28 @@
         <v>1490</v>
       </c>
       <c r="M3">
-        <v>22.4670483</v>
+        <v>44.9340966</v>
       </c>
       <c r="N3">
-        <v>1467.5329517</v>
+        <v>1445.0659034</v>
       </c>
       <c r="O3">
-        <v>183.4416189625</v>
+        <v>180.633237925</v>
       </c>
       <c r="P3">
-        <v>1284.0913327375</v>
+        <v>1264.432665475</v>
       </c>
       <c r="Q3">
-        <v>1998.0913327375</v>
+        <v>1978.432665475</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09515088170719743</v>
+        <v>0.09559206606002416</v>
       </c>
       <c r="T3">
-        <v>0.9619405412210945</v>
+        <v>0.9705400454336913</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>66.31934823409803</v>
+        <v>33.15967411704901</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09456047473882367</v>
+        <v>0.09448145158752187</v>
       </c>
       <c r="C4">
-        <v>43768.83484910309</v>
+        <v>43394.27489768773</v>
       </c>
       <c r="D4">
-        <v>44417.15684910309</v>
+        <v>44489.25789768773</v>
       </c>
       <c r="E4">
-        <v>-4304.678</v>
+        <v>-3858.017</v>
       </c>
       <c r="F4">
-        <v>893.322</v>
+        <v>1339.983</v>
       </c>
       <c r="G4">
         <v>245</v>
@@ -1621,28 +1621,28 @@
         <v>1490</v>
       </c>
       <c r="M4">
-        <v>44.9340966</v>
+        <v>67.40114489999999</v>
       </c>
       <c r="N4">
-        <v>1445.0659034</v>
+        <v>1422.5988551</v>
       </c>
       <c r="O4">
-        <v>180.633237925</v>
+        <v>177.8248568875</v>
       </c>
       <c r="P4">
-        <v>1264.432665475</v>
+        <v>1244.7739982125</v>
       </c>
       <c r="Q4">
-        <v>1978.432665475</v>
+        <v>1958.7739982125</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09559206606002416</v>
+        <v>0.09604234699744524</v>
       </c>
       <c r="T4">
-        <v>0.9705400454336913</v>
+        <v>0.9793168590114965</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>33.15967411704901</v>
+        <v>22.10644941136601</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09448145158752187</v>
+        <v>0.0944024284362201</v>
       </c>
       <c r="C5">
-        <v>43394.27489768773</v>
+        <v>43019.94940583556</v>
       </c>
       <c r="D5">
-        <v>44489.25789768773</v>
+        <v>44561.59340583556</v>
       </c>
       <c r="E5">
-        <v>-3858.017</v>
+        <v>-3411.356</v>
       </c>
       <c r="F5">
-        <v>1339.983</v>
+        <v>1786.644</v>
       </c>
       <c r="G5">
         <v>245</v>
@@ -1703,28 +1703,28 @@
         <v>1490</v>
       </c>
       <c r="M5">
-        <v>67.40114489999999</v>
+        <v>89.86819319999999</v>
       </c>
       <c r="N5">
-        <v>1422.5988551</v>
+        <v>1400.1318068</v>
       </c>
       <c r="O5">
-        <v>177.8248568875</v>
+        <v>175.01647585</v>
       </c>
       <c r="P5">
-        <v>1244.7739982125</v>
+        <v>1225.11533095</v>
       </c>
       <c r="Q5">
-        <v>1958.7739982125</v>
+        <v>1939.11533095</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09604234699744524</v>
+        <v>0.09650200878772927</v>
       </c>
       <c r="T5">
-        <v>0.9793168590114965</v>
+        <v>0.9882765228721725</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>22.10644941136601</v>
+        <v>16.57983705852451</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0944024284362201</v>
+        <v>0.09432340528491831</v>
       </c>
       <c r="C6">
-        <v>43019.94940583556</v>
+        <v>42645.8595190392</v>
       </c>
       <c r="D6">
-        <v>44561.59340583556</v>
+        <v>44634.1645190392</v>
       </c>
       <c r="E6">
-        <v>-3411.356</v>
+        <v>-2964.695</v>
       </c>
       <c r="F6">
-        <v>1786.644</v>
+        <v>2233.305</v>
       </c>
       <c r="G6">
         <v>245</v>
@@ -1785,28 +1785,28 @@
         <v>1490</v>
       </c>
       <c r="M6">
-        <v>89.86819319999999</v>
+        <v>112.3352415</v>
       </c>
       <c r="N6">
-        <v>1400.1318068</v>
+        <v>1377.6647585</v>
       </c>
       <c r="O6">
-        <v>175.01647585</v>
+        <v>172.2080948125</v>
       </c>
       <c r="P6">
-        <v>1225.11533095</v>
+        <v>1205.4566636875</v>
       </c>
       <c r="Q6">
-        <v>1939.11533095</v>
+        <v>1919.4566636875</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09650200878772927</v>
+        <v>0.09697134766833507</v>
       </c>
       <c r="T6">
-        <v>0.9882765228721725</v>
+        <v>0.9974248112351787</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>16.57983705852451</v>
+        <v>13.26386964681961</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09432340528491831</v>
+        <v>0.09424438213361654</v>
       </c>
       <c r="C7">
-        <v>42645.8595190392</v>
+        <v>42272.00639026538</v>
       </c>
       <c r="D7">
-        <v>44634.1645190392</v>
+        <v>44706.97239026538</v>
       </c>
       <c r="E7">
-        <v>-2964.695</v>
+        <v>-2518.034</v>
       </c>
       <c r="F7">
-        <v>2233.305</v>
+        <v>2679.966</v>
       </c>
       <c r="G7">
         <v>245</v>
@@ -1867,28 +1867,28 @@
         <v>1490</v>
       </c>
       <c r="M7">
-        <v>112.3352415</v>
+        <v>134.8022898</v>
       </c>
       <c r="N7">
-        <v>1377.6647585</v>
+        <v>1355.1977102</v>
       </c>
       <c r="O7">
-        <v>172.2080948125</v>
+        <v>169.399713775</v>
       </c>
       <c r="P7">
-        <v>1205.4566636875</v>
+        <v>1185.797996425</v>
       </c>
       <c r="Q7">
-        <v>1919.4566636875</v>
+        <v>1899.797996425</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09697134766833507</v>
+        <v>0.09745067248257079</v>
       </c>
       <c r="T7">
-        <v>0.9974248112351787</v>
+        <v>1.00676774403144</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>13.26386964681961</v>
+        <v>11.053224705683</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09424438213361654</v>
+        <v>0.09416535898231476</v>
       </c>
       <c r="C8">
-        <v>42272.00639026538</v>
+        <v>41898.39118001611</v>
       </c>
       <c r="D8">
-        <v>44706.97239026538</v>
+        <v>44780.01818001611</v>
       </c>
       <c r="E8">
-        <v>-2518.034</v>
+        <v>-2071.373000000001</v>
       </c>
       <c r="F8">
-        <v>2679.966</v>
+        <v>3126.626999999999</v>
       </c>
       <c r="G8">
         <v>245</v>
@@ -1949,28 +1949,28 @@
         <v>1490</v>
       </c>
       <c r="M8">
-        <v>134.8022898</v>
+        <v>157.2693381</v>
       </c>
       <c r="N8">
-        <v>1355.1977102</v>
+        <v>1332.7306619</v>
       </c>
       <c r="O8">
-        <v>169.399713775</v>
+        <v>166.5913327375</v>
       </c>
       <c r="P8">
-        <v>1185.797996425</v>
+        <v>1166.1393291625</v>
       </c>
       <c r="Q8">
-        <v>1899.797996425</v>
+        <v>1880.1393291625</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09745067248257079</v>
+        <v>0.0979403053573277</v>
       </c>
       <c r="T8">
-        <v>1.00676774403144</v>
+        <v>1.016311600113643</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>11.05322470568301</v>
+        <v>9.474192604871149</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09416535898231475</v>
+        <v>0.09419133583101297</v>
       </c>
       <c r="C9">
-        <v>41898.39118001611</v>
+        <v>41427.6919149633</v>
       </c>
       <c r="D9">
-        <v>44780.01818001612</v>
+        <v>44755.9799149633</v>
       </c>
       <c r="E9">
-        <v>-2071.373</v>
+        <v>-1624.712</v>
       </c>
       <c r="F9">
-        <v>3126.627</v>
+        <v>3573.288</v>
       </c>
       <c r="G9">
         <v>245</v>
@@ -2031,45 +2031,45 @@
         <v>1490</v>
       </c>
       <c r="M9">
-        <v>157.2693381</v>
+        <v>185.0963184</v>
       </c>
       <c r="N9">
-        <v>1332.7306619</v>
+        <v>1304.9036816</v>
       </c>
       <c r="O9">
-        <v>166.5913327375</v>
+        <v>163.1129602</v>
       </c>
       <c r="P9">
-        <v>1166.1393291625</v>
+        <v>1141.7907214</v>
       </c>
       <c r="Q9">
-        <v>1880.1393291625</v>
+        <v>1855.7907214</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0979403053573277</v>
+        <v>0.09844058242501409</v>
       </c>
       <c r="T9">
-        <v>1.016311600113643</v>
+        <v>1.026062931328067</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.125</v>
       </c>
       <c r="W9">
-        <v>0.0440125</v>
+        <v>0.045325</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>9.474192604871147</v>
+        <v>8.049862973395586</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09419133583101297</v>
+        <v>0.09412543767971118</v>
       </c>
       <c r="C10">
-        <v>41427.6919149633</v>
+        <v>41042.06163662264</v>
       </c>
       <c r="D10">
-        <v>44755.9799149633</v>
+        <v>44817.01063662264</v>
       </c>
       <c r="E10">
-        <v>-1624.712</v>
+        <v>-1178.051</v>
       </c>
       <c r="F10">
-        <v>3573.288</v>
+        <v>4019.949</v>
       </c>
       <c r="G10">
         <v>245</v>
@@ -2113,28 +2113,28 @@
         <v>1490</v>
       </c>
       <c r="M10">
-        <v>185.0963184</v>
+        <v>208.2333582</v>
       </c>
       <c r="N10">
-        <v>1304.9036816</v>
+        <v>1281.7666418</v>
       </c>
       <c r="O10">
-        <v>163.1129602</v>
+        <v>160.220830225</v>
       </c>
       <c r="P10">
-        <v>1141.7907214</v>
+        <v>1121.545811575</v>
       </c>
       <c r="Q10">
-        <v>1855.7907214</v>
+        <v>1835.545811575</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09844058242501409</v>
+        <v>0.09895185459308919</v>
       </c>
       <c r="T10">
-        <v>1.026062931328067</v>
+        <v>1.036028577514237</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>8.049862973395586</v>
+        <v>7.155433754129411</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09412543767971118</v>
+        <v>0.0942082895284094</v>
       </c>
       <c r="C11">
-        <v>41042.06163662264</v>
+        <v>40518.69534047304</v>
       </c>
       <c r="D11">
-        <v>44817.01063662264</v>
+        <v>44740.30534047304</v>
       </c>
       <c r="E11">
-        <v>-1178.051</v>
+        <v>-731.3900000000003</v>
       </c>
       <c r="F11">
-        <v>4019.949</v>
+        <v>4466.61</v>
       </c>
       <c r="G11">
         <v>245</v>
@@ -2195,45 +2195,45 @@
         <v>1490</v>
       </c>
       <c r="M11">
-        <v>208.2333582</v>
+        <v>238.963635</v>
       </c>
       <c r="N11">
-        <v>1281.7666418</v>
+        <v>1251.036365</v>
       </c>
       <c r="O11">
-        <v>160.220830225</v>
+        <v>156.379545625</v>
       </c>
       <c r="P11">
-        <v>1121.545811575</v>
+        <v>1094.656819375</v>
       </c>
       <c r="Q11">
-        <v>1835.545811575</v>
+        <v>1808.656819375</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09895185459308919</v>
+        <v>0.09947448836489933</v>
       </c>
       <c r="T11">
-        <v>1.036028577514237</v>
+        <v>1.046215682504545</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.125</v>
       </c>
       <c r="W11">
-        <v>0.045325</v>
+        <v>0.0468125</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>7.155433754129411</v>
+        <v>6.235258347990898</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.0942082895284094</v>
+        <v>0.0941572663771076</v>
       </c>
       <c r="C12">
-        <v>40518.69534047304</v>
+        <v>40119.24113150365</v>
       </c>
       <c r="D12">
-        <v>44740.30534047304</v>
+        <v>44787.51213150365</v>
       </c>
       <c r="E12">
-        <v>-731.3900000000003</v>
+        <v>-284.7290000000003</v>
       </c>
       <c r="F12">
-        <v>4466.61</v>
+        <v>4913.271</v>
       </c>
       <c r="G12">
         <v>245</v>
@@ -2277,28 +2277,28 @@
         <v>1490</v>
       </c>
       <c r="M12">
-        <v>238.963635</v>
+        <v>262.8599985</v>
       </c>
       <c r="N12">
-        <v>1251.036365</v>
+        <v>1227.1400015</v>
       </c>
       <c r="O12">
-        <v>156.379545625</v>
+        <v>153.3925001875</v>
       </c>
       <c r="P12">
-        <v>1094.656819375</v>
+        <v>1073.7475013125</v>
       </c>
       <c r="Q12">
-        <v>1808.656819375</v>
+        <v>1787.7475013125</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09947448836489933</v>
+        <v>0.1000088667158512</v>
       </c>
       <c r="T12">
-        <v>1.046215682504545</v>
+        <v>1.056631711202499</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>6.235258347990898</v>
+        <v>5.668416679991726</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0941572663771076</v>
+        <v>0.09419024322580584</v>
       </c>
       <c r="C13">
-        <v>40119.24113150365</v>
+        <v>39642.05846199604</v>
       </c>
       <c r="D13">
-        <v>44787.51213150365</v>
+        <v>44756.99046199604</v>
       </c>
       <c r="E13">
-        <v>-284.7290000000003</v>
+        <v>161.9319999999998</v>
       </c>
       <c r="F13">
-        <v>4913.271</v>
+        <v>5359.932</v>
       </c>
       <c r="G13">
         <v>245</v>
@@ -2359,45 +2359,45 @@
         <v>1490</v>
       </c>
       <c r="M13">
-        <v>262.8599985</v>
+        <v>291.0443076</v>
       </c>
       <c r="N13">
-        <v>1227.1400015</v>
+        <v>1198.9556924</v>
       </c>
       <c r="O13">
-        <v>153.3925001875</v>
+        <v>149.86946155</v>
       </c>
       <c r="P13">
-        <v>1073.7475013125</v>
+        <v>1049.08623085</v>
       </c>
       <c r="Q13">
-        <v>1787.7475013125</v>
+        <v>1763.08623085</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1000088667158512</v>
+        <v>0.1005553900293248</v>
       </c>
       <c r="T13">
-        <v>1.056631711202499</v>
+        <v>1.067284467825407</v>
       </c>
       <c r="U13">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V13">
         <v>0.125</v>
       </c>
       <c r="W13">
-        <v>0.0468125</v>
+        <v>0.0475125</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y13">
-        <v>5.668416679991726</v>
+        <v>5.119495420772147</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09419024322580584</v>
+        <v>0.09414622007450406</v>
       </c>
       <c r="C14">
-        <v>39642.05846199604</v>
+        <v>39236.15232886845</v>
       </c>
       <c r="D14">
-        <v>44756.99046199604</v>
+        <v>44797.74532886845</v>
       </c>
       <c r="E14">
-        <v>161.9319999999998</v>
+        <v>608.5929999999998</v>
       </c>
       <c r="F14">
-        <v>5359.932</v>
+        <v>5806.593</v>
       </c>
       <c r="G14">
         <v>245</v>
@@ -2441,28 +2441,28 @@
         <v>1490</v>
       </c>
       <c r="M14">
-        <v>291.0443076</v>
+        <v>315.2979999</v>
       </c>
       <c r="N14">
-        <v>1198.9556924</v>
+        <v>1174.7020001</v>
       </c>
       <c r="O14">
-        <v>149.86946155</v>
+        <v>146.8377500125</v>
       </c>
       <c r="P14">
-        <v>1049.08623085</v>
+        <v>1027.8642500875</v>
       </c>
       <c r="Q14">
-        <v>1763.08623085</v>
+        <v>1741.8642500875</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1005553900293248</v>
+        <v>0.1011144770971311</v>
       </c>
       <c r="T14">
-        <v>1.067284467825407</v>
+        <v>1.078182115405164</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.119495420772147</v>
+        <v>4.725688080712751</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09414622007450406</v>
+        <v>0.09410219692320225</v>
       </c>
       <c r="C15">
-        <v>39236.15232886845</v>
+        <v>38830.32048460496</v>
       </c>
       <c r="D15">
-        <v>44797.74532886845</v>
+        <v>44838.57448460496</v>
       </c>
       <c r="E15">
-        <v>608.5929999999998</v>
+        <v>1055.254000000001</v>
       </c>
       <c r="F15">
-        <v>5806.593</v>
+        <v>6253.254000000001</v>
       </c>
       <c r="G15">
         <v>245</v>
@@ -2523,28 +2523,28 @@
         <v>1490</v>
       </c>
       <c r="M15">
-        <v>315.2979999</v>
+        <v>339.5516922</v>
       </c>
       <c r="N15">
-        <v>1174.7020001</v>
+        <v>1150.4483078</v>
       </c>
       <c r="O15">
-        <v>146.8377500125</v>
+        <v>143.806038475</v>
       </c>
       <c r="P15">
-        <v>1027.8642500875</v>
+        <v>1006.642269325</v>
       </c>
       <c r="Q15">
-        <v>1741.8642500875</v>
+        <v>1720.642269325</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1011144770971311</v>
+        <v>0.1016865661897701</v>
       </c>
       <c r="T15">
-        <v>1.078182115405164</v>
+        <v>1.089333196649565</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>4.725688080712751</v>
+        <v>4.38813893209041</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09410219692320225</v>
+        <v>0.09418942377190048</v>
       </c>
       <c r="C16">
-        <v>38830.32048460496</v>
+        <v>38302.83340221866</v>
       </c>
       <c r="D16">
-        <v>44838.57448460496</v>
+        <v>44757.74840221866</v>
       </c>
       <c r="E16">
-        <v>1055.254000000001</v>
+        <v>1501.915000000001</v>
       </c>
       <c r="F16">
-        <v>6253.254000000001</v>
+        <v>6699.915000000001</v>
       </c>
       <c r="G16">
         <v>245</v>
@@ -2605,45 +2605,45 @@
         <v>1490</v>
       </c>
       <c r="M16">
-        <v>339.5516922</v>
+        <v>370.5052995</v>
       </c>
       <c r="N16">
-        <v>1150.4483078</v>
+        <v>1119.4947005</v>
       </c>
       <c r="O16">
-        <v>143.806038475</v>
+        <v>139.9368375625</v>
       </c>
       <c r="P16">
-        <v>1006.642269325</v>
+        <v>979.5578629375</v>
       </c>
       <c r="Q16">
-        <v>1720.642269325</v>
+        <v>1693.5578629375</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1016865661897701</v>
+        <v>0.1022721162022359</v>
       </c>
       <c r="T16">
-        <v>1.089333196649565</v>
+        <v>1.100746656276189</v>
       </c>
       <c r="U16">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V16">
         <v>0.125</v>
       </c>
       <c r="W16">
-        <v>0.0475125</v>
+        <v>0.0483875</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.38813893209041</v>
+        <v>4.021534920042351</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09418942377190047</v>
+        <v>0.09415415062059869</v>
       </c>
       <c r="C17">
-        <v>38302.83340221867</v>
+        <v>37888.82206747089</v>
       </c>
       <c r="D17">
-        <v>44757.74840221867</v>
+        <v>44790.39806747089</v>
       </c>
       <c r="E17">
-        <v>1501.915</v>
+        <v>1948.576</v>
       </c>
       <c r="F17">
-        <v>6699.915</v>
+        <v>7146.576</v>
       </c>
       <c r="G17">
         <v>245</v>
@@ -2687,28 +2687,28 @@
         <v>1490</v>
       </c>
       <c r="M17">
-        <v>370.5052995</v>
+        <v>395.2056528</v>
       </c>
       <c r="N17">
-        <v>1119.4947005</v>
+        <v>1094.7943472</v>
       </c>
       <c r="O17">
-        <v>139.9368375625</v>
+        <v>136.8492934</v>
       </c>
       <c r="P17">
-        <v>979.5578629375</v>
+        <v>957.9450538</v>
       </c>
       <c r="Q17">
-        <v>1693.5578629375</v>
+        <v>1671.9450538</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1022721162022358</v>
+        <v>0.1028716078816651</v>
       </c>
       <c r="T17">
-        <v>1.100746656276189</v>
+        <v>1.112431864941541</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>4.021534920042351</v>
+        <v>3.770188987539704</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09415415062059869</v>
+        <v>0.0941188774692969</v>
       </c>
       <c r="C18">
-        <v>37888.82206747089</v>
+        <v>37474.85840173545</v>
       </c>
       <c r="D18">
-        <v>44790.39806747089</v>
+        <v>44823.09540173545</v>
       </c>
       <c r="E18">
-        <v>1948.576</v>
+        <v>2395.237</v>
       </c>
       <c r="F18">
-        <v>7146.576</v>
+        <v>7593.237</v>
       </c>
       <c r="G18">
         <v>245</v>
@@ -2769,28 +2769,28 @@
         <v>1490</v>
       </c>
       <c r="M18">
-        <v>395.2056528</v>
+        <v>419.9060061</v>
       </c>
       <c r="N18">
-        <v>1094.7943472</v>
+        <v>1070.0939939</v>
       </c>
       <c r="O18">
-        <v>136.8492934</v>
+        <v>133.7617492375</v>
       </c>
       <c r="P18">
-        <v>957.9450538</v>
+        <v>936.3322446625</v>
       </c>
       <c r="Q18">
-        <v>1671.9450538</v>
+        <v>1650.3322446625</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1028716078816651</v>
+        <v>0.1034855451437312</v>
       </c>
       <c r="T18">
-        <v>1.112431864941541</v>
+        <v>1.124398644900034</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>3.770188987539704</v>
+        <v>3.548413164743251</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0941188774692969</v>
+        <v>0.09408360431799513</v>
       </c>
       <c r="C19">
-        <v>37474.85840173545</v>
+        <v>37060.94250948478</v>
       </c>
       <c r="D19">
-        <v>44823.09540173545</v>
+        <v>44855.84050948478</v>
       </c>
       <c r="E19">
-        <v>2395.237</v>
+        <v>2841.898000000001</v>
       </c>
       <c r="F19">
-        <v>7593.237</v>
+        <v>8039.898000000001</v>
       </c>
       <c r="G19">
         <v>245</v>
@@ -2851,28 +2851,28 @@
         <v>1490</v>
       </c>
       <c r="M19">
-        <v>419.9060061</v>
+        <v>444.6063594000001</v>
       </c>
       <c r="N19">
-        <v>1070.0939939</v>
+        <v>1045.3936406</v>
       </c>
       <c r="O19">
-        <v>133.7617492375</v>
+        <v>130.674205075</v>
       </c>
       <c r="P19">
-        <v>936.3322446625</v>
+        <v>914.7194355249999</v>
       </c>
       <c r="Q19">
-        <v>1650.3322446625</v>
+        <v>1628.719435525</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1034855451437312</v>
+        <v>0.1041144564853599</v>
       </c>
       <c r="T19">
-        <v>1.124398644900034</v>
+        <v>1.136657297540442</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.548413164743251</v>
+        <v>3.351279100035292</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09408360431799513</v>
+        <v>0.09404833116669334</v>
       </c>
       <c r="C20">
-        <v>37060.94250948478</v>
+        <v>36647.07449549695</v>
       </c>
       <c r="D20">
-        <v>44855.84050948478</v>
+        <v>44888.63349549695</v>
       </c>
       <c r="E20">
-        <v>2841.897999999999</v>
+        <v>3288.558999999999</v>
       </c>
       <c r="F20">
-        <v>8039.897999999999</v>
+        <v>8486.558999999999</v>
       </c>
       <c r="G20">
         <v>245</v>
@@ -2933,28 +2933,28 @@
         <v>1490</v>
       </c>
       <c r="M20">
-        <v>444.6063594</v>
+        <v>469.3067127</v>
       </c>
       <c r="N20">
-        <v>1045.3936406</v>
+        <v>1020.6932873</v>
       </c>
       <c r="O20">
-        <v>130.674205075</v>
+        <v>127.5866609125</v>
       </c>
       <c r="P20">
-        <v>914.719435525</v>
+        <v>893.1066263875</v>
       </c>
       <c r="Q20">
-        <v>1628.719435525</v>
+        <v>1607.1066263875</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1041144564853599</v>
+        <v>0.1047588965020905</v>
       </c>
       <c r="T20">
-        <v>1.136657297540442</v>
+        <v>1.149218632962095</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.351279100035293</v>
+        <v>3.17489598950712</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09404833116669334</v>
+        <v>0.09401305801539157</v>
       </c>
       <c r="C21">
-        <v>36647.07449549695</v>
+        <v>36233.25446485656</v>
       </c>
       <c r="D21">
-        <v>44888.63349549695</v>
+        <v>44921.47446485656</v>
       </c>
       <c r="E21">
-        <v>3288.558999999999</v>
+        <v>3735.219999999999</v>
       </c>
       <c r="F21">
-        <v>8486.558999999999</v>
+        <v>8933.219999999999</v>
       </c>
       <c r="G21">
         <v>245</v>
@@ -3015,28 +3015,28 @@
         <v>1490</v>
       </c>
       <c r="M21">
-        <v>469.3067127</v>
+        <v>494.007066</v>
       </c>
       <c r="N21">
-        <v>1020.6932873</v>
+        <v>995.992934</v>
       </c>
       <c r="O21">
-        <v>127.5866609125</v>
+        <v>124.49911675</v>
       </c>
       <c r="P21">
-        <v>893.1066263875</v>
+        <v>871.49381725</v>
       </c>
       <c r="Q21">
-        <v>1607.1066263875</v>
+        <v>1585.49381725</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1047588965020905</v>
+        <v>0.1054194475192395</v>
       </c>
       <c r="T21">
-        <v>1.149218632962095</v>
+        <v>1.162094001769288</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.17489598950712</v>
+        <v>3.016151190031763</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09401305801539157</v>
+        <v>0.09443715986408978</v>
       </c>
       <c r="C22">
-        <v>36233.25446485656</v>
+        <v>35394.89130913794</v>
       </c>
       <c r="D22">
-        <v>44921.47446485656</v>
+        <v>44529.77230913794</v>
       </c>
       <c r="E22">
-        <v>3735.219999999999</v>
+        <v>4181.881000000001</v>
       </c>
       <c r="F22">
-        <v>8933.219999999999</v>
+        <v>9379.881000000001</v>
       </c>
       <c r="G22">
         <v>245</v>
@@ -3097,45 +3097,45 @@
         <v>1490</v>
       </c>
       <c r="M22">
-        <v>494.007066</v>
+        <v>542.1571218000001</v>
       </c>
       <c r="N22">
-        <v>995.992934</v>
+        <v>947.8428781999999</v>
       </c>
       <c r="O22">
-        <v>124.49911675</v>
+        <v>118.480359775</v>
       </c>
       <c r="P22">
-        <v>871.49381725</v>
+        <v>829.3625184249998</v>
       </c>
       <c r="Q22">
-        <v>1585.49381725</v>
+        <v>1543.362518425</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1054194475192395</v>
+        <v>0.1060967213469491</v>
       </c>
       <c r="T22">
-        <v>1.162094001769288</v>
+        <v>1.175295329280462</v>
       </c>
       <c r="U22">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V22">
         <v>0.125</v>
       </c>
       <c r="W22">
-        <v>0.0483875</v>
+        <v>0.050575</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.016151190031763</v>
+        <v>2.748280784458008</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09443715986408975</v>
+        <v>0.09442376171278799</v>
       </c>
       <c r="C23">
-        <v>35394.89130913797</v>
+        <v>34960.50037228846</v>
       </c>
       <c r="D23">
-        <v>44529.77230913797</v>
+        <v>44542.04237228847</v>
       </c>
       <c r="E23">
-        <v>4181.880999999999</v>
+        <v>4628.541999999999</v>
       </c>
       <c r="F23">
-        <v>9379.880999999999</v>
+        <v>9826.541999999999</v>
       </c>
       <c r="G23">
         <v>245</v>
@@ -3179,28 +3179,28 @@
         <v>1490</v>
       </c>
       <c r="M23">
-        <v>542.1571218</v>
+        <v>567.9741276</v>
       </c>
       <c r="N23">
-        <v>947.8428782</v>
+        <v>922.0258724</v>
       </c>
       <c r="O23">
-        <v>118.480359775</v>
+        <v>115.25323405</v>
       </c>
       <c r="P23">
-        <v>829.362518425</v>
+        <v>806.7726383500001</v>
       </c>
       <c r="Q23">
-        <v>1543.362518425</v>
+        <v>1520.77263835</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1060967213469491</v>
+        <v>0.106791361170241</v>
       </c>
       <c r="T23">
-        <v>1.175295329280462</v>
+        <v>1.188835152368845</v>
       </c>
       <c r="U23">
         <v>0.0578</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.748280784458008</v>
+        <v>2.623358930619008</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09442376171278799</v>
+        <v>0.0944103635614862</v>
       </c>
       <c r="C24">
-        <v>34960.50037228846</v>
+        <v>34526.11619927083</v>
       </c>
       <c r="D24">
-        <v>44542.04237228847</v>
+        <v>44554.31919927083</v>
       </c>
       <c r="E24">
-        <v>4628.541999999999</v>
+        <v>5075.203</v>
       </c>
       <c r="F24">
-        <v>9826.541999999999</v>
+        <v>10273.203</v>
       </c>
       <c r="G24">
         <v>245</v>
@@ -3261,28 +3261,28 @@
         <v>1490</v>
       </c>
       <c r="M24">
-        <v>567.9741276</v>
+        <v>593.7911334</v>
       </c>
       <c r="N24">
-        <v>922.0258724</v>
+        <v>896.2088666</v>
       </c>
       <c r="O24">
-        <v>115.25323405</v>
+        <v>112.026108325</v>
       </c>
       <c r="P24">
-        <v>806.7726383500001</v>
+        <v>784.182758275</v>
       </c>
       <c r="Q24">
-        <v>1520.77263835</v>
+        <v>1498.182758275</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.106791361170241</v>
+        <v>0.1075040435863457</v>
       </c>
       <c r="T24">
-        <v>1.188835152368845</v>
+        <v>1.202726659173809</v>
       </c>
       <c r="U24">
         <v>0.0578</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.623358930619008</v>
+        <v>2.509299846679051</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0944103635614862</v>
+        <v>0.09513196541018441</v>
       </c>
       <c r="C25">
-        <v>34526.11619927083</v>
+        <v>33427.73822764078</v>
       </c>
       <c r="D25">
-        <v>44554.31919927083</v>
+        <v>43902.60222764078</v>
       </c>
       <c r="E25">
-        <v>5075.203</v>
+        <v>5521.864000000001</v>
       </c>
       <c r="F25">
-        <v>10273.203</v>
+        <v>10719.864</v>
       </c>
       <c r="G25">
         <v>245</v>
@@ -3343,45 +3343,45 @@
         <v>1490</v>
       </c>
       <c r="M25">
-        <v>593.7911334</v>
+        <v>657.1276632000001</v>
       </c>
       <c r="N25">
-        <v>896.2088666</v>
+        <v>832.8723367999999</v>
       </c>
       <c r="O25">
-        <v>112.026108325</v>
+        <v>104.1090421</v>
       </c>
       <c r="P25">
-        <v>784.182758275</v>
+        <v>728.7632946999998</v>
       </c>
       <c r="Q25">
-        <v>1498.182758275</v>
+        <v>1442.7632947</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1075040435863457</v>
+        <v>0.1082354808028742</v>
       </c>
       <c r="T25">
-        <v>1.202726659173809</v>
+        <v>1.216983731947325</v>
       </c>
       <c r="U25">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V25">
         <v>0.125</v>
       </c>
       <c r="W25">
-        <v>0.050575</v>
+        <v>0.0536375</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.509299846679051</v>
+        <v>2.267443730407239</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09513196541018441</v>
+        <v>0.09576169225888263</v>
       </c>
       <c r="C26">
-        <v>33427.73822764078</v>
+        <v>32427.72032357097</v>
       </c>
       <c r="D26">
-        <v>43902.60222764078</v>
+        <v>43349.24532357098</v>
       </c>
       <c r="E26">
-        <v>5521.864</v>
+        <v>5968.525</v>
       </c>
       <c r="F26">
-        <v>10719.864</v>
+        <v>11166.525</v>
       </c>
       <c r="G26">
         <v>245</v>
@@ -3425,45 +3425,45 @@
         <v>1490</v>
       </c>
       <c r="M26">
-        <v>657.1276632</v>
+        <v>715.7742525</v>
       </c>
       <c r="N26">
-        <v>832.8723368</v>
+        <v>774.2257475</v>
       </c>
       <c r="O26">
-        <v>104.1090421</v>
+        <v>96.7782184375</v>
       </c>
       <c r="P26">
-        <v>728.7632947</v>
+        <v>677.4475290625001</v>
       </c>
       <c r="Q26">
-        <v>1442.7632947</v>
+        <v>1391.4475290625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1082354808028742</v>
+        <v>0.1089864230118435</v>
       </c>
       <c r="T26">
-        <v>1.216983731947325</v>
+        <v>1.231620993328135</v>
       </c>
       <c r="U26">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V26">
         <v>0.125</v>
       </c>
       <c r="W26">
-        <v>0.0536375</v>
+        <v>0.05608750000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.267443730407239</v>
+        <v>2.081661913369816</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09576169225888263</v>
+        <v>0.09580341910758085</v>
       </c>
       <c r="C27">
-        <v>32427.72032357097</v>
+        <v>31944.88524921604</v>
       </c>
       <c r="D27">
-        <v>43349.24532357098</v>
+        <v>43313.07124921605</v>
       </c>
       <c r="E27">
-        <v>5968.525</v>
+        <v>6415.186</v>
       </c>
       <c r="F27">
-        <v>11166.525</v>
+        <v>11613.186</v>
       </c>
       <c r="G27">
         <v>245</v>
@@ -3507,28 +3507,28 @@
         <v>1490</v>
       </c>
       <c r="M27">
-        <v>715.7742525</v>
+        <v>744.4052226</v>
       </c>
       <c r="N27">
-        <v>774.2257475</v>
+        <v>745.5947774</v>
       </c>
       <c r="O27">
-        <v>96.7782184375</v>
+        <v>93.199347175</v>
       </c>
       <c r="P27">
-        <v>677.4475290625001</v>
+        <v>652.395430225</v>
       </c>
       <c r="Q27">
-        <v>1391.4475290625</v>
+        <v>1366.395430225</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1089864230118435</v>
+        <v>0.1097576609561903</v>
       </c>
       <c r="T27">
-        <v>1.231620993328135</v>
+        <v>1.246653856367885</v>
       </c>
       <c r="U27">
         <v>0.0641</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.081661913369816</v>
+        <v>2.001597993624824</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09580341910758085</v>
+        <v>0.09860927095627907</v>
       </c>
       <c r="C28">
-        <v>31944.88524921604</v>
+        <v>29196.92262477162</v>
       </c>
       <c r="D28">
-        <v>43313.07124921605</v>
+        <v>41011.76962477162</v>
       </c>
       <c r="E28">
-        <v>6415.186</v>
+        <v>6861.847</v>
       </c>
       <c r="F28">
-        <v>11613.186</v>
+        <v>12059.847</v>
       </c>
       <c r="G28">
         <v>245</v>
@@ -3589,45 +3589,45 @@
         <v>1490</v>
       </c>
       <c r="M28">
-        <v>744.4052226</v>
+        <v>914.1364026000001</v>
       </c>
       <c r="N28">
-        <v>745.5947774</v>
+        <v>575.8635973999999</v>
       </c>
       <c r="O28">
-        <v>93.199347175</v>
+        <v>71.98294967499999</v>
       </c>
       <c r="P28">
-        <v>652.395430225</v>
+        <v>503.8806477249999</v>
       </c>
       <c r="Q28">
-        <v>1366.395430225</v>
+        <v>1217.880647725</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1097576609561903</v>
+        <v>0.1105500287072316</v>
       </c>
       <c r="T28">
-        <v>1.246653856367885</v>
+        <v>1.262098578668999</v>
       </c>
       <c r="U28">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V28">
         <v>0.125</v>
       </c>
       <c r="W28">
-        <v>0.05608750000000001</v>
+        <v>0.06632500000000001</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.001597993624824</v>
+        <v>1.629953687176356</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09860927095627907</v>
+        <v>0.09875337280497729</v>
       </c>
       <c r="C29">
-        <v>29196.92262477162</v>
+        <v>28638.65642366232</v>
       </c>
       <c r="D29">
-        <v>41011.76962477162</v>
+        <v>40900.16442366233</v>
       </c>
       <c r="E29">
-        <v>6861.847</v>
+        <v>7308.508000000002</v>
       </c>
       <c r="F29">
-        <v>12059.847</v>
+        <v>12506.508</v>
       </c>
       <c r="G29">
         <v>245</v>
@@ -3671,28 +3671,28 @@
         <v>1490</v>
       </c>
       <c r="M29">
-        <v>914.1364026000001</v>
+        <v>947.9933064000002</v>
       </c>
       <c r="N29">
-        <v>575.8635973999999</v>
+        <v>542.0066935999998</v>
       </c>
       <c r="O29">
-        <v>71.98294967499999</v>
+        <v>67.75083669999998</v>
       </c>
       <c r="P29">
-        <v>503.8806477249999</v>
+        <v>474.2558568999999</v>
       </c>
       <c r="Q29">
-        <v>1217.880647725</v>
+        <v>1188.2558569</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1105500287072316</v>
+        <v>0.1113644066735796</v>
       </c>
       <c r="T29">
-        <v>1.262098578668999</v>
+        <v>1.277972321034032</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>1.629953687176356</v>
+        <v>1.571741055491486</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09875337280497729</v>
+        <v>0.0988974746536755</v>
       </c>
       <c r="C30">
-        <v>28638.65642366232</v>
+        <v>28080.99599583732</v>
       </c>
       <c r="D30">
-        <v>40900.16442366233</v>
+        <v>40789.16499583732</v>
       </c>
       <c r="E30">
-        <v>7308.508000000002</v>
+        <v>7755.169000000002</v>
       </c>
       <c r="F30">
-        <v>12506.508</v>
+        <v>12953.169</v>
       </c>
       <c r="G30">
         <v>245</v>
@@ -3753,28 +3753,28 @@
         <v>1490</v>
       </c>
       <c r="M30">
-        <v>947.9933064000002</v>
+        <v>981.8502102000002</v>
       </c>
       <c r="N30">
-        <v>542.0066935999998</v>
+        <v>508.1497897999998</v>
       </c>
       <c r="O30">
-        <v>67.75083669999998</v>
+        <v>63.51872372499997</v>
       </c>
       <c r="P30">
-        <v>474.2558568999999</v>
+        <v>444.6310660749998</v>
       </c>
       <c r="Q30">
-        <v>1188.2558569</v>
+        <v>1158.631066075</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1113644066735796</v>
+        <v>0.1122017248643317</v>
       </c>
       <c r="T30">
-        <v>1.277972321034032</v>
+        <v>1.29429321107132</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>1.571741055491486</v>
+        <v>1.517543088060745</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09889747465367549</v>
+        <v>0.1106687774456203</v>
       </c>
       <c r="C31">
-        <v>28080.99599583733</v>
+        <v>20232.59827898455</v>
       </c>
       <c r="D31">
-        <v>40789.16499583733</v>
+        <v>33387.42827898455</v>
       </c>
       <c r="E31">
-        <v>7755.168999999998</v>
+        <v>8201.83</v>
       </c>
       <c r="F31">
-        <v>12953.169</v>
+        <v>13399.83</v>
       </c>
       <c r="G31">
         <v>245</v>
@@ -3835,45 +3835,45 @@
         <v>1490</v>
       </c>
       <c r="M31">
-        <v>981.8502101999999</v>
+        <v>1589.219838</v>
       </c>
       <c r="N31">
-        <v>508.1497898000001</v>
+        <v>-99.21983800000021</v>
       </c>
       <c r="O31">
-        <v>63.51872372500002</v>
+        <v>-12.40247975000003</v>
       </c>
       <c r="P31">
-        <v>444.6310660750001</v>
+        <v>-86.81735825000018</v>
       </c>
       <c r="Q31">
-        <v>1158.631066075</v>
+        <v>627.1826417499998</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1122017248643317</v>
+        <v>0.1132265806654847</v>
       </c>
       <c r="T31">
-        <v>1.29429321107132</v>
+        <v>1.314269558198891</v>
       </c>
       <c r="U31">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V31">
-        <v>0.125</v>
+        <v>0.1171958690336962</v>
       </c>
       <c r="W31">
-        <v>0.06632500000000001</v>
+        <v>0.1047005699326036</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y31">
-        <v>1.517543088060746</v>
+        <v>0.93756695226957</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1106687774456203</v>
+        <v>0.1113967774456203</v>
       </c>
       <c r="C32">
-        <v>20232.59827898455</v>
+        <v>19415.4000554563</v>
       </c>
       <c r="D32">
-        <v>33387.42827898455</v>
+        <v>33016.8910554563</v>
       </c>
       <c r="E32">
-        <v>8201.83</v>
+        <v>8648.491</v>
       </c>
       <c r="F32">
-        <v>13399.83</v>
+        <v>13846.491</v>
       </c>
       <c r="G32">
         <v>245</v>
@@ -3917,37 +3917,37 @@
         <v>1490</v>
       </c>
       <c r="M32">
-        <v>1589.219838</v>
+        <v>1642.1938326</v>
       </c>
       <c r="N32">
-        <v>-99.21983800000021</v>
+        <v>-152.1938326000002</v>
       </c>
       <c r="O32">
-        <v>-12.40247975000003</v>
+        <v>-19.02422907500002</v>
       </c>
       <c r="P32">
-        <v>-86.81735825000018</v>
+        <v>-133.1696035250002</v>
       </c>
       <c r="Q32">
-        <v>627.1826417499998</v>
+        <v>580.8303964749998</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1132265806654847</v>
+        <v>0.1142037774867236</v>
       </c>
       <c r="T32">
-        <v>1.314269558198891</v>
+        <v>1.333316943100325</v>
       </c>
       <c r="U32">
         <v>0.1186</v>
       </c>
       <c r="V32">
-        <v>0.1171958690336962</v>
+        <v>0.1134153571293835</v>
       </c>
       <c r="W32">
-        <v>0.1047005699326036</v>
+        <v>0.1051489386444551</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.93756695226957</v>
+        <v>0.9073228570350678</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1113967774456203</v>
+        <v>0.1121247774456204</v>
       </c>
       <c r="C33">
-        <v>19415.4000554563</v>
+        <v>18606.3360800663</v>
       </c>
       <c r="D33">
-        <v>33016.8910554563</v>
+        <v>32654.4880800663</v>
       </c>
       <c r="E33">
-        <v>8648.491</v>
+        <v>9095.152</v>
       </c>
       <c r="F33">
-        <v>13846.491</v>
+        <v>14293.152</v>
       </c>
       <c r="G33">
         <v>245</v>
@@ -3999,37 +3999,37 @@
         <v>1490</v>
       </c>
       <c r="M33">
-        <v>1642.1938326</v>
+        <v>1695.1678272</v>
       </c>
       <c r="N33">
-        <v>-152.1938326000002</v>
+        <v>-205.1678272000001</v>
       </c>
       <c r="O33">
-        <v>-19.02422907500002</v>
+        <v>-25.64597840000002</v>
       </c>
       <c r="P33">
-        <v>-133.1696035250002</v>
+        <v>-179.5218488000001</v>
       </c>
       <c r="Q33">
-        <v>580.8303964749998</v>
+        <v>534.4781511999998</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1142037774867236</v>
+        <v>0.1152097153909401</v>
       </c>
       <c r="T33">
-        <v>1.333316943100325</v>
+        <v>1.352924545204741</v>
       </c>
       <c r="U33">
         <v>0.1186</v>
       </c>
       <c r="V33">
-        <v>0.1134153571293835</v>
+        <v>0.1098711272190902</v>
       </c>
       <c r="W33">
-        <v>0.1051489386444551</v>
+        <v>0.1055692843118159</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.9073228570350678</v>
+        <v>0.878969017752722</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1121247774456204</v>
+        <v>0.1128527774456204</v>
       </c>
       <c r="C34">
-        <v>18606.3360800663</v>
+        <v>17805.14140930869</v>
       </c>
       <c r="D34">
-        <v>32654.4880800663</v>
+        <v>32299.9544093087</v>
       </c>
       <c r="E34">
-        <v>9095.152</v>
+        <v>9541.813</v>
       </c>
       <c r="F34">
-        <v>14293.152</v>
+        <v>14739.813</v>
       </c>
       <c r="G34">
         <v>245</v>
@@ -4081,37 +4081,37 @@
         <v>1490</v>
       </c>
       <c r="M34">
-        <v>1695.1678272</v>
+        <v>1748.1418218</v>
       </c>
       <c r="N34">
-        <v>-205.1678272000001</v>
+        <v>-258.1418218000001</v>
       </c>
       <c r="O34">
-        <v>-25.64597840000002</v>
+        <v>-32.26772772500001</v>
       </c>
       <c r="P34">
-        <v>-179.5218488000001</v>
+        <v>-225.8740940750001</v>
       </c>
       <c r="Q34">
-        <v>534.4781511999998</v>
+        <v>488.1259059249999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1152097153909401</v>
+        <v>0.1162456812922974</v>
       </c>
       <c r="T34">
-        <v>1.352924545204741</v>
+        <v>1.373117448864513</v>
       </c>
       <c r="U34">
         <v>0.1186</v>
       </c>
       <c r="V34">
-        <v>0.1098711272190902</v>
+        <v>0.1065416991215421</v>
       </c>
       <c r="W34">
-        <v>0.1055692843118159</v>
+        <v>0.1059641544841851</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.878969017752722</v>
+        <v>0.8523335929723365</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1128527774456204</v>
+        <v>0.1135807774456203</v>
       </c>
       <c r="C35">
-        <v>17805.14140930869</v>
+        <v>17011.5624821893</v>
       </c>
       <c r="D35">
-        <v>32299.9544093087</v>
+        <v>31953.0364821893</v>
       </c>
       <c r="E35">
-        <v>9541.813</v>
+        <v>9988.474</v>
       </c>
       <c r="F35">
-        <v>14739.813</v>
+        <v>15186.474</v>
       </c>
       <c r="G35">
         <v>245</v>
@@ -4163,37 +4163,37 @@
         <v>1490</v>
       </c>
       <c r="M35">
-        <v>1748.1418218</v>
+        <v>1801.1158164</v>
       </c>
       <c r="N35">
-        <v>-258.1418218000001</v>
+        <v>-311.1158164000001</v>
       </c>
       <c r="O35">
-        <v>-32.26772772500001</v>
+        <v>-38.88947705000001</v>
       </c>
       <c r="P35">
-        <v>-225.8740940750001</v>
+        <v>-272.2263393500001</v>
       </c>
       <c r="Q35">
-        <v>488.1259059249999</v>
+        <v>441.7736606499999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1162456812922974</v>
+        <v>0.1173130400997565</v>
       </c>
       <c r="T35">
-        <v>1.373117448864513</v>
+        <v>1.393922258695794</v>
       </c>
       <c r="U35">
         <v>0.1186</v>
       </c>
       <c r="V35">
-        <v>0.1065416991215421</v>
+        <v>0.1034081197356144</v>
       </c>
       <c r="W35">
-        <v>0.1059641544841851</v>
+        <v>0.1063357969993561</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.8523335929723365</v>
+        <v>0.8272649578849148</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1135807774456203</v>
+        <v>0.1143087774456204</v>
       </c>
       <c r="C36">
-        <v>17011.5624821893</v>
+        <v>16225.3565154513</v>
       </c>
       <c r="D36">
-        <v>31953.0364821893</v>
+        <v>31613.4915154513</v>
       </c>
       <c r="E36">
-        <v>9988.474</v>
+        <v>10435.135</v>
       </c>
       <c r="F36">
-        <v>15186.474</v>
+        <v>15633.135</v>
       </c>
       <c r="G36">
         <v>245</v>
@@ -4245,37 +4245,37 @@
         <v>1490</v>
       </c>
       <c r="M36">
-        <v>1801.1158164</v>
+        <v>1854.089811</v>
       </c>
       <c r="N36">
-        <v>-311.1158164000001</v>
+        <v>-364.0898110000003</v>
       </c>
       <c r="O36">
-        <v>-38.88947705000001</v>
+        <v>-45.51122637500004</v>
       </c>
       <c r="P36">
-        <v>-272.2263393500001</v>
+        <v>-318.5785846250002</v>
       </c>
       <c r="Q36">
-        <v>441.7736606499999</v>
+        <v>395.4214153749998</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1173130400997565</v>
+        <v>0.1184132407166758</v>
       </c>
       <c r="T36">
-        <v>1.393922258695794</v>
+        <v>1.415367216521883</v>
       </c>
       <c r="U36">
         <v>0.1186</v>
       </c>
       <c r="V36">
-        <v>0.1034081197356144</v>
+        <v>0.1004536020288825</v>
       </c>
       <c r="W36">
-        <v>0.1063357969993561</v>
+        <v>0.1066862027993745</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8272649578849148</v>
+        <v>0.80362881623106</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1143087774456204</v>
+        <v>0.1453328460617226</v>
       </c>
       <c r="C37">
-        <v>16225.3565154513</v>
+        <v>5924.871689679003</v>
       </c>
       <c r="D37">
-        <v>31613.4915154513</v>
+        <v>21759.667689679</v>
       </c>
       <c r="E37">
-        <v>10435.135</v>
+        <v>10881.796</v>
       </c>
       <c r="F37">
-        <v>15633.135</v>
+        <v>16079.796</v>
       </c>
       <c r="G37">
         <v>245</v>
@@ -4327,45 +4327,45 @@
         <v>1490</v>
       </c>
       <c r="M37">
-        <v>1854.089811</v>
+        <v>3228.8230368</v>
       </c>
       <c r="N37">
-        <v>-364.0898110000003</v>
+        <v>-1738.8230368</v>
       </c>
       <c r="O37">
-        <v>-45.51122637500004</v>
+        <v>-217.3528796000001</v>
       </c>
       <c r="P37">
-        <v>-318.5785846250002</v>
+        <v>-1521.4701572</v>
       </c>
       <c r="Q37">
-        <v>395.4214153749998</v>
+        <v>-807.4701572000004</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1184132407166758</v>
+        <v>0.1206479298155336</v>
       </c>
       <c r="T37">
-        <v>1.415367216521883</v>
+        <v>1.458925466483254</v>
       </c>
       <c r="U37">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V37">
-        <v>0.1004536020288825</v>
+        <v>0.05768355771661843</v>
       </c>
       <c r="W37">
-        <v>0.1066862027993745</v>
+        <v>0.189217141610503</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y37">
-        <v>0.80362881623106</v>
+        <v>0.4614684617329474</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1453328460617226</v>
+        <v>0.1468828460617226</v>
       </c>
       <c r="C38">
-        <v>5924.871689679014</v>
+        <v>5144.548884208994</v>
       </c>
       <c r="D38">
-        <v>21759.66768967901</v>
+        <v>21426.00588420899</v>
       </c>
       <c r="E38">
-        <v>10881.796</v>
+        <v>11328.457</v>
       </c>
       <c r="F38">
-        <v>16079.796</v>
+        <v>16526.457</v>
       </c>
       <c r="G38">
         <v>245</v>
@@ -4409,37 +4409,37 @@
         <v>1490</v>
       </c>
       <c r="M38">
-        <v>3228.8230368</v>
+        <v>3318.5125656</v>
       </c>
       <c r="N38">
-        <v>-1738.8230368</v>
+        <v>-1828.5125656</v>
       </c>
       <c r="O38">
-        <v>-217.3528796</v>
+        <v>-228.5640707</v>
       </c>
       <c r="P38">
-        <v>-1521.4701572</v>
+        <v>-1599.9484949</v>
       </c>
       <c r="Q38">
-        <v>-807.4701571999999</v>
+        <v>-885.9484949</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1206479298155336</v>
+        <v>0.121835992193558</v>
       </c>
       <c r="T38">
-        <v>1.458925466483254</v>
+        <v>1.48208301357029</v>
       </c>
       <c r="U38">
         <v>0.2008</v>
       </c>
       <c r="V38">
-        <v>0.05768355771661843</v>
+        <v>0.05612454264319632</v>
       </c>
       <c r="W38">
-        <v>0.189217141610503</v>
+        <v>0.1895301918372462</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.4614684617329474</v>
+        <v>0.4489963411455705</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1468828460617226</v>
+        <v>0.1484328460617226</v>
       </c>
       <c r="C39">
-        <v>5144.548884208994</v>
+        <v>4374.304251922778</v>
       </c>
       <c r="D39">
-        <v>21426.00588420899</v>
+        <v>21102.42225192278</v>
       </c>
       <c r="E39">
-        <v>11328.457</v>
+        <v>11775.118</v>
       </c>
       <c r="F39">
-        <v>16526.457</v>
+        <v>16973.118</v>
       </c>
       <c r="G39">
         <v>245</v>
@@ -4491,37 +4491,37 @@
         <v>1490</v>
       </c>
       <c r="M39">
-        <v>3318.5125656</v>
+        <v>3408.2020944</v>
       </c>
       <c r="N39">
-        <v>-1828.5125656</v>
+        <v>-1918.2020944</v>
       </c>
       <c r="O39">
-        <v>-228.5640707</v>
+        <v>-239.7752618</v>
       </c>
       <c r="P39">
-        <v>-1599.9484949</v>
+        <v>-1678.4268326</v>
       </c>
       <c r="Q39">
-        <v>-885.9484949</v>
+        <v>-964.4268325999997</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.121835992193558</v>
+        <v>0.1230623791644218</v>
       </c>
       <c r="T39">
-        <v>1.48208301357029</v>
+        <v>1.505987578305295</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.05612454264319632</v>
+        <v>0.05464758099469115</v>
       </c>
       <c r="W39">
-        <v>0.1895301918372462</v>
+        <v>0.189826765736266</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.4489963411455705</v>
+        <v>0.4371806479575292</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1484328460617226</v>
+        <v>0.1499828460617226</v>
       </c>
       <c r="C40">
-        <v>4374.304251922778</v>
+        <v>3613.687973036442</v>
       </c>
       <c r="D40">
-        <v>21102.42225192278</v>
+        <v>20788.46697303644</v>
       </c>
       <c r="E40">
-        <v>11775.118</v>
+        <v>12221.779</v>
       </c>
       <c r="F40">
-        <v>16973.118</v>
+        <v>17419.779</v>
       </c>
       <c r="G40">
         <v>245</v>
@@ -4573,37 +4573,37 @@
         <v>1490</v>
       </c>
       <c r="M40">
-        <v>3408.2020944</v>
+        <v>3497.8916232</v>
       </c>
       <c r="N40">
-        <v>-1918.2020944</v>
+        <v>-2007.8916232</v>
       </c>
       <c r="O40">
-        <v>-239.7752618</v>
+        <v>-250.9864529</v>
       </c>
       <c r="P40">
-        <v>-1678.4268326</v>
+        <v>-1756.9051703</v>
       </c>
       <c r="Q40">
-        <v>-964.4268325999997</v>
+        <v>-1042.9051703</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1230623791644218</v>
+        <v>0.1243289755441664</v>
       </c>
       <c r="T40">
-        <v>1.505987578305295</v>
+        <v>1.530675899261119</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.05464758099469115</v>
+        <v>0.05324636096918625</v>
       </c>
       <c r="W40">
-        <v>0.189826765736266</v>
+        <v>0.1901081307173874</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4371806479575292</v>
+        <v>0.42597088775349</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1499828460617226</v>
+        <v>0.1515328460617226</v>
       </c>
       <c r="C41">
-        <v>3613.687973036442</v>
+        <v>2862.276604457533</v>
       </c>
       <c r="D41">
-        <v>20788.46697303644</v>
+        <v>20483.71660445753</v>
       </c>
       <c r="E41">
-        <v>12221.779</v>
+        <v>12668.44</v>
       </c>
       <c r="F41">
-        <v>17419.779</v>
+        <v>17866.44</v>
       </c>
       <c r="G41">
         <v>245</v>
@@ -4655,37 +4655,37 @@
         <v>1490</v>
       </c>
       <c r="M41">
-        <v>3497.8916232</v>
+        <v>3587.581152</v>
       </c>
       <c r="N41">
-        <v>-2007.8916232</v>
+        <v>-2097.581152</v>
       </c>
       <c r="O41">
-        <v>-250.9864529</v>
+        <v>-262.197644</v>
       </c>
       <c r="P41">
-        <v>-1756.9051703</v>
+        <v>-1835.383508</v>
       </c>
       <c r="Q41">
-        <v>-1042.9051703</v>
+        <v>-1121.383508</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1243289755441664</v>
+        <v>0.1256377918032359</v>
       </c>
       <c r="T41">
-        <v>1.530675899261119</v>
+        <v>1.556187164248804</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.05324636096918625</v>
+        <v>0.05191520194495659</v>
       </c>
       <c r="W41">
-        <v>0.1901081307173874</v>
+        <v>0.1903754274494527</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.42597088775349</v>
+        <v>0.4153216155596527</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1515328460617226</v>
+        <v>0.1530828460617226</v>
       </c>
       <c r="C42">
-        <v>2862.276604457533</v>
+        <v>2119.671174360647</v>
       </c>
       <c r="D42">
-        <v>20483.71660445753</v>
+        <v>20187.77217436065</v>
       </c>
       <c r="E42">
-        <v>12668.44</v>
+        <v>13115.101</v>
       </c>
       <c r="F42">
-        <v>17866.44</v>
+        <v>18313.101</v>
       </c>
       <c r="G42">
         <v>245</v>
@@ -4737,37 +4737,37 @@
         <v>1490</v>
       </c>
       <c r="M42">
-        <v>3587.581152</v>
+        <v>3677.270680800001</v>
       </c>
       <c r="N42">
-        <v>-2097.581152</v>
+        <v>-2187.270680800001</v>
       </c>
       <c r="O42">
-        <v>-262.197644</v>
+        <v>-273.4088351000001</v>
       </c>
       <c r="P42">
-        <v>-1835.383508</v>
+        <v>-1913.861845700001</v>
       </c>
       <c r="Q42">
-        <v>-1121.383508</v>
+        <v>-1199.861845700001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1256377918032359</v>
+        <v>0.1269909747151551</v>
       </c>
       <c r="T42">
-        <v>1.556187164248804</v>
+        <v>1.58256321788014</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.05191520194495659</v>
+        <v>0.05064897750727471</v>
       </c>
       <c r="W42">
-        <v>0.1903754274494527</v>
+        <v>0.1906296853165392</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.4153216155596527</v>
+        <v>0.4051918200581976</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1530828460617226</v>
+        <v>0.1546328460617226</v>
       </c>
       <c r="C43">
-        <v>2119.671174360647</v>
+        <v>1385.495439585509</v>
       </c>
       <c r="D43">
-        <v>20187.77217436065</v>
+        <v>19900.25743958551</v>
       </c>
       <c r="E43">
-        <v>13115.101</v>
+        <v>13561.762</v>
       </c>
       <c r="F43">
-        <v>18313.101</v>
+        <v>18759.762</v>
       </c>
       <c r="G43">
         <v>245</v>
@@ -4819,37 +4819,37 @@
         <v>1490</v>
       </c>
       <c r="M43">
-        <v>3677.270680800001</v>
+        <v>3766.960209600001</v>
       </c>
       <c r="N43">
-        <v>-2187.270680800001</v>
+        <v>-2276.960209600001</v>
       </c>
       <c r="O43">
-        <v>-273.4088351000001</v>
+        <v>-284.6200262000001</v>
       </c>
       <c r="P43">
-        <v>-1913.861845700001</v>
+        <v>-1992.340183400001</v>
       </c>
       <c r="Q43">
-        <v>-1199.861845700001</v>
+        <v>-1278.340183400001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1269909747151551</v>
+        <v>0.1283908191067957</v>
       </c>
       <c r="T43">
-        <v>1.58256321788014</v>
+        <v>1.609848790602212</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.05064897750727471</v>
+        <v>0.04944304947138722</v>
       </c>
       <c r="W43">
-        <v>0.1906296853165392</v>
+        <v>0.1908718356661455</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.4051918200581976</v>
+        <v>0.3955443957710978</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1546328460617226</v>
+        <v>0.1561828460617226</v>
       </c>
       <c r="C44">
-        <v>1385.495439585513</v>
+        <v>659.3942898532805</v>
       </c>
       <c r="D44">
-        <v>19900.25743958551</v>
+        <v>19620.81728985328</v>
       </c>
       <c r="E44">
-        <v>13561.762</v>
+        <v>14008.423</v>
       </c>
       <c r="F44">
-        <v>18759.762</v>
+        <v>19206.423</v>
       </c>
       <c r="G44">
         <v>245</v>
@@ -4901,37 +4901,37 @@
         <v>1490</v>
       </c>
       <c r="M44">
-        <v>3766.9602096</v>
+        <v>3856.6497384</v>
       </c>
       <c r="N44">
-        <v>-2276.9602096</v>
+        <v>-2366.6497384</v>
       </c>
       <c r="O44">
-        <v>-284.6200262</v>
+        <v>-295.8312173</v>
       </c>
       <c r="P44">
-        <v>-1992.3401834</v>
+        <v>-2070.8185211</v>
       </c>
       <c r="Q44">
-        <v>-1278.3401834</v>
+        <v>-1356.8185211</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1283908191067957</v>
+        <v>0.1298397808455114</v>
       </c>
       <c r="T44">
-        <v>1.609848790602211</v>
+        <v>1.638091751840847</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.04944304947138723</v>
+        <v>0.04829321111158753</v>
       </c>
       <c r="W44">
-        <v>0.1908718356661455</v>
+        <v>0.1911027232087932</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3955443957710978</v>
+        <v>0.3863456888927002</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1561828460617226</v>
+        <v>0.1577328460617226</v>
       </c>
       <c r="C45">
-        <v>659.3942898532805</v>
+        <v>-58.9677154307501</v>
       </c>
       <c r="D45">
-        <v>19620.81728985328</v>
+        <v>19349.11628456925</v>
       </c>
       <c r="E45">
-        <v>14008.423</v>
+        <v>14455.084</v>
       </c>
       <c r="F45">
-        <v>19206.423</v>
+        <v>19653.084</v>
       </c>
       <c r="G45">
         <v>245</v>
@@ -4983,37 +4983,37 @@
         <v>1490</v>
       </c>
       <c r="M45">
-        <v>3856.6497384</v>
+        <v>3946.3392672</v>
       </c>
       <c r="N45">
-        <v>-2366.6497384</v>
+        <v>-2456.3392672</v>
       </c>
       <c r="O45">
-        <v>-295.8312173</v>
+        <v>-307.0424084</v>
       </c>
       <c r="P45">
-        <v>-2070.8185211</v>
+        <v>-2149.2968588</v>
       </c>
       <c r="Q45">
-        <v>-1356.8185211</v>
+        <v>-1435.2968588</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1298397808455114</v>
+        <v>0.1313404912177527</v>
       </c>
       <c r="T45">
-        <v>1.638091751840847</v>
+        <v>1.667343390266576</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.04829321111158753</v>
+        <v>0.04719563813177872</v>
       </c>
       <c r="W45">
-        <v>0.1911027232087932</v>
+        <v>0.1913231158631388</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3863456888927002</v>
+        <v>0.3775651050542297</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1577328460617226</v>
+        <v>0.1592828460617226</v>
       </c>
       <c r="C46">
-        <v>-58.9677154307501</v>
+        <v>-769.9076904643007</v>
       </c>
       <c r="D46">
-        <v>19349.11628456925</v>
+        <v>19084.8373095357</v>
       </c>
       <c r="E46">
-        <v>14455.084</v>
+        <v>14901.745</v>
       </c>
       <c r="F46">
-        <v>19653.084</v>
+        <v>20099.745</v>
       </c>
       <c r="G46">
         <v>245</v>
@@ -5065,37 +5065,37 @@
         <v>1490</v>
       </c>
       <c r="M46">
-        <v>3946.3392672</v>
+        <v>4036.028796</v>
       </c>
       <c r="N46">
-        <v>-2456.3392672</v>
+        <v>-2546.028796</v>
       </c>
       <c r="O46">
-        <v>-307.0424084</v>
+        <v>-318.2535995</v>
       </c>
       <c r="P46">
-        <v>-2149.2968588</v>
+        <v>-2227.7751965</v>
       </c>
       <c r="Q46">
-        <v>-1435.2968588</v>
+        <v>-1513.7751965</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1313404912177527</v>
+        <v>0.1328957728762573</v>
       </c>
       <c r="T46">
-        <v>1.667343390266576</v>
+        <v>1.697658724635059</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.04719563813177872</v>
+        <v>0.04614684617329474</v>
       </c>
       <c r="W46">
-        <v>0.1913231158631388</v>
+        <v>0.1915337132884024</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3775651050542297</v>
+        <v>0.369174769386358</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1592828460617226</v>
+        <v>0.1608328460617226</v>
       </c>
       <c r="C47">
-        <v>-769.9076904643007</v>
+        <v>-1473.725657735264</v>
       </c>
       <c r="D47">
-        <v>19084.8373095357</v>
+        <v>18827.68034226474</v>
       </c>
       <c r="E47">
-        <v>14901.745</v>
+        <v>15348.406</v>
       </c>
       <c r="F47">
-        <v>20099.745</v>
+        <v>20546.406</v>
       </c>
       <c r="G47">
         <v>245</v>
@@ -5147,37 +5147,37 @@
         <v>1490</v>
       </c>
       <c r="M47">
-        <v>4036.028796</v>
+        <v>4125.7183248</v>
       </c>
       <c r="N47">
-        <v>-2546.028796</v>
+        <v>-2635.7183248</v>
       </c>
       <c r="O47">
-        <v>-318.2535995</v>
+        <v>-329.4647906</v>
       </c>
       <c r="P47">
-        <v>-2227.7751965</v>
+        <v>-2306.2535342</v>
       </c>
       <c r="Q47">
-        <v>-1513.7751965</v>
+        <v>-1592.2535342</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1328957728762573</v>
+        <v>0.134508657559151</v>
       </c>
       <c r="T47">
-        <v>1.697658724635059</v>
+        <v>1.729096849165338</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.04614684617329474</v>
+        <v>0.04514365386517964</v>
       </c>
       <c r="W47">
-        <v>0.1915337132884024</v>
+        <v>0.1917351543038719</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.369174769386358</v>
+        <v>0.3611492309214371</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1608328460617226</v>
+        <v>0.1623828460617226</v>
       </c>
       <c r="C48">
-        <v>-1473.725657735264</v>
+        <v>-2170.705684215885</v>
       </c>
       <c r="D48">
-        <v>18827.68034226474</v>
+        <v>18577.36131578411</v>
       </c>
       <c r="E48">
-        <v>15348.406</v>
+        <v>15795.067</v>
       </c>
       <c r="F48">
-        <v>20546.406</v>
+        <v>20993.067</v>
       </c>
       <c r="G48">
         <v>245</v>
@@ -5229,37 +5229,37 @@
         <v>1490</v>
       </c>
       <c r="M48">
-        <v>4125.7183248</v>
+        <v>4215.4078536</v>
       </c>
       <c r="N48">
-        <v>-2635.7183248</v>
+        <v>-2725.4078536</v>
       </c>
       <c r="O48">
-        <v>-329.4647906</v>
+        <v>-340.6759817</v>
       </c>
       <c r="P48">
-        <v>-2306.2535342</v>
+        <v>-2384.7318719</v>
       </c>
       <c r="Q48">
-        <v>-1592.2535342</v>
+        <v>-1670.7318719</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.134508657559151</v>
+        <v>0.136182405814984</v>
       </c>
       <c r="T48">
-        <v>1.729096849165338</v>
+        <v>1.761721318017515</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.04514365386517964</v>
+        <v>0.04418315059145242</v>
       </c>
       <c r="W48">
-        <v>0.1917351543038719</v>
+        <v>0.1919280233612364</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3611492309214371</v>
+        <v>0.3534652047316194</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1623828460617226</v>
+        <v>0.1639328460617226</v>
       </c>
       <c r="C49">
-        <v>-2170.705684215885</v>
+        <v>-2861.116928110128</v>
       </c>
       <c r="D49">
-        <v>18577.36131578411</v>
+        <v>18333.61107188987</v>
       </c>
       <c r="E49">
-        <v>15795.067</v>
+        <v>16241.728</v>
       </c>
       <c r="F49">
-        <v>20993.067</v>
+        <v>21439.728</v>
       </c>
       <c r="G49">
         <v>245</v>
@@ -5311,37 +5311,37 @@
         <v>1490</v>
       </c>
       <c r="M49">
-        <v>4215.4078536</v>
+        <v>4305.0973824</v>
       </c>
       <c r="N49">
-        <v>-2725.4078536</v>
+        <v>-2815.0973824</v>
       </c>
       <c r="O49">
-        <v>-340.6759817</v>
+        <v>-351.8871728</v>
       </c>
       <c r="P49">
-        <v>-2384.7318719</v>
+        <v>-2463.2102096</v>
       </c>
       <c r="Q49">
-        <v>-1670.7318719</v>
+        <v>-1749.2102096</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.136182405814984</v>
+        <v>0.1379205290037337</v>
       </c>
       <c r="T49">
-        <v>1.761721318017515</v>
+        <v>1.795600574133236</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.04418315059145242</v>
+        <v>0.04326266828746382</v>
       </c>
       <c r="W49">
-        <v>0.1919280233612364</v>
+        <v>0.1921128562078773</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3534652047316194</v>
+        <v>0.3461013462997106</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1639328460617226</v>
+        <v>0.1654828460617226</v>
       </c>
       <c r="C50">
-        <v>-2861.116928110117</v>
+        <v>-3545.214604263143</v>
       </c>
       <c r="D50">
-        <v>18333.61107188988</v>
+        <v>18096.17439573686</v>
       </c>
       <c r="E50">
-        <v>16241.728</v>
+        <v>16688.389</v>
       </c>
       <c r="F50">
-        <v>21439.728</v>
+        <v>21886.389</v>
       </c>
       <c r="G50">
         <v>245</v>
@@ -5393,37 +5393,37 @@
         <v>1490</v>
       </c>
       <c r="M50">
-        <v>4305.0973824</v>
+        <v>4394.7869112</v>
       </c>
       <c r="N50">
-        <v>-2815.0973824</v>
+        <v>-2904.7869112</v>
       </c>
       <c r="O50">
-        <v>-351.8871728</v>
+        <v>-363.0983639</v>
       </c>
       <c r="P50">
-        <v>-2463.2102096</v>
+        <v>-2541.6885473</v>
       </c>
       <c r="Q50">
-        <v>-1749.2102096</v>
+        <v>-1827.6885473</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1379205290037337</v>
+        <v>0.1397268138861598</v>
       </c>
       <c r="T50">
-        <v>1.795600574133236</v>
+        <v>1.830808428528005</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.04326266828746382</v>
+        <v>0.04237975668976048</v>
       </c>
       <c r="W50">
-        <v>0.1921128562078773</v>
+        <v>0.1922901448566961</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3461013462997106</v>
+        <v>0.3390380535180838</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1654828460617226</v>
+        <v>0.1670328460617226</v>
       </c>
       <c r="C51">
-        <v>-3545.214604263143</v>
+        <v>-4223.240875512423</v>
       </c>
       <c r="D51">
-        <v>18096.17439573686</v>
+        <v>17864.80912448758</v>
       </c>
       <c r="E51">
-        <v>16688.389</v>
+        <v>17135.05</v>
       </c>
       <c r="F51">
-        <v>21886.389</v>
+        <v>22333.05</v>
       </c>
       <c r="G51">
         <v>245</v>
@@ -5475,37 +5475,37 @@
         <v>1490</v>
       </c>
       <c r="M51">
-        <v>4394.7869112</v>
+        <v>4484.47644</v>
       </c>
       <c r="N51">
-        <v>-2904.7869112</v>
+        <v>-2994.47644</v>
       </c>
       <c r="O51">
-        <v>-363.0983639</v>
+        <v>-374.309555</v>
       </c>
       <c r="P51">
-        <v>-2541.6885473</v>
+        <v>-2620.166885000001</v>
       </c>
       <c r="Q51">
-        <v>-1827.6885473</v>
+        <v>-1906.166885000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1397268138861598</v>
+        <v>0.141605350163883</v>
       </c>
       <c r="T51">
-        <v>1.830808428528005</v>
+        <v>1.867424597098565</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.04237975668976048</v>
+        <v>0.04153216155596526</v>
       </c>
       <c r="W51">
-        <v>0.1922901448566961</v>
+        <v>0.1924603419595622</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3390380535180838</v>
+        <v>0.3322572924477222</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1670328460617226</v>
+        <v>0.1685828460617226</v>
       </c>
       <c r="C52">
-        <v>-4223.240875512423</v>
+        <v>-4895.425676524785</v>
       </c>
       <c r="D52">
-        <v>17864.80912448758</v>
+        <v>17639.28532347521</v>
       </c>
       <c r="E52">
-        <v>17135.05</v>
+        <v>17581.711</v>
       </c>
       <c r="F52">
-        <v>22333.05</v>
+        <v>22779.711</v>
       </c>
       <c r="G52">
         <v>245</v>
@@ -5557,37 +5557,37 @@
         <v>1490</v>
       </c>
       <c r="M52">
-        <v>4484.47644</v>
+        <v>4574.1659688</v>
       </c>
       <c r="N52">
-        <v>-2994.47644</v>
+        <v>-3084.1659688</v>
       </c>
       <c r="O52">
-        <v>-374.309555</v>
+        <v>-385.5207461</v>
       </c>
       <c r="P52">
-        <v>-2620.166885000001</v>
+        <v>-2698.6452227</v>
       </c>
       <c r="Q52">
-        <v>-1906.166885000001</v>
+        <v>-1984.6452227</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.141605350163883</v>
+        <v>0.1435605613917174</v>
       </c>
       <c r="T52">
-        <v>1.867424597098565</v>
+        <v>1.905535303161801</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.04153216155596526</v>
+        <v>0.04071780544702477</v>
       </c>
       <c r="W52">
-        <v>0.1924603419595622</v>
+        <v>0.1926238646662374</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3322572924477222</v>
+        <v>0.3257424435761982</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1685828460617226</v>
+        <v>0.1701328460617226</v>
       </c>
       <c r="C53">
-        <v>-4895.425676524785</v>
+        <v>-5561.987476011138</v>
       </c>
       <c r="D53">
-        <v>17639.28532347521</v>
+        <v>17419.38452398886</v>
       </c>
       <c r="E53">
-        <v>17581.711</v>
+        <v>18028.372</v>
       </c>
       <c r="F53">
-        <v>22779.711</v>
+        <v>23226.372</v>
       </c>
       <c r="G53">
         <v>245</v>
@@ -5639,37 +5639,37 @@
         <v>1490</v>
       </c>
       <c r="M53">
-        <v>4574.1659688</v>
+        <v>4663.8554976</v>
       </c>
       <c r="N53">
-        <v>-3084.1659688</v>
+        <v>-3173.8554976</v>
       </c>
       <c r="O53">
-        <v>-385.5207461</v>
+        <v>-396.7319371999999</v>
       </c>
       <c r="P53">
-        <v>-2698.6452227</v>
+        <v>-2777.123560399999</v>
       </c>
       <c r="Q53">
-        <v>-1984.6452227</v>
+        <v>-2063.123560399999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1435605613917174</v>
+        <v>0.1455972397540448</v>
       </c>
       <c r="T53">
-        <v>1.905535303161801</v>
+        <v>1.945233955311006</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.04071780544702477</v>
+        <v>0.03993477072688969</v>
       </c>
       <c r="W53">
-        <v>0.1926238646662374</v>
+        <v>0.1927810980380406</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3257424435761982</v>
+        <v>0.3194781658151175</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1701328460617226</v>
+        <v>0.1716828460617226</v>
       </c>
       <c r="C54">
-        <v>-5561.987476011138</v>
+        <v>-6223.133982630075</v>
       </c>
       <c r="D54">
-        <v>17419.38452398886</v>
+        <v>17204.89901736992</v>
       </c>
       <c r="E54">
-        <v>18028.372</v>
+        <v>18475.033</v>
       </c>
       <c r="F54">
-        <v>23226.372</v>
+        <v>23673.033</v>
       </c>
       <c r="G54">
         <v>245</v>
@@ -5721,37 +5721,37 @@
         <v>1490</v>
       </c>
       <c r="M54">
-        <v>4663.8554976</v>
+        <v>4753.5450264</v>
       </c>
       <c r="N54">
-        <v>-3173.8554976</v>
+        <v>-3263.5450264</v>
       </c>
       <c r="O54">
-        <v>-396.7319371999999</v>
+        <v>-407.9431283</v>
       </c>
       <c r="P54">
-        <v>-2777.123560399999</v>
+        <v>-2855.6018981</v>
       </c>
       <c r="Q54">
-        <v>-2063.123560399999</v>
+        <v>-2141.6018981</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1455972397540448</v>
+        <v>0.1477205852807266</v>
       </c>
       <c r="T54">
-        <v>1.945233955311006</v>
+        <v>1.986621911806984</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.03993477072688969</v>
+        <v>0.03918128448675969</v>
       </c>
       <c r="W54">
-        <v>0.1927810980380406</v>
+        <v>0.1929323980750587</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3194781658151175</v>
+        <v>0.3134502758940775</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1716828460617226</v>
+        <v>0.1732328460617226</v>
       </c>
       <c r="C55">
-        <v>-6223.133982630075</v>
+        <v>-6879.062799374966</v>
       </c>
       <c r="D55">
-        <v>17204.89901736992</v>
+        <v>16995.63120062503</v>
       </c>
       <c r="E55">
-        <v>18475.033</v>
+        <v>18921.694</v>
       </c>
       <c r="F55">
-        <v>23673.033</v>
+        <v>24119.694</v>
       </c>
       <c r="G55">
         <v>245</v>
@@ -5803,37 +5803,37 @@
         <v>1490</v>
       </c>
       <c r="M55">
-        <v>4753.5450264</v>
+        <v>4843.2345552</v>
       </c>
       <c r="N55">
-        <v>-3263.5450264</v>
+        <v>-3353.2345552</v>
       </c>
       <c r="O55">
-        <v>-407.9431283</v>
+        <v>-419.1543194</v>
       </c>
       <c r="P55">
-        <v>-2855.6018981</v>
+        <v>-2934.0802358</v>
       </c>
       <c r="Q55">
-        <v>-2141.6018981</v>
+        <v>-2220.0802358</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1477205852807266</v>
+        <v>0.1499362501781338</v>
       </c>
       <c r="T55">
-        <v>1.986621911806984</v>
+        <v>2.029809344672354</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.03918128448675969</v>
+        <v>0.03845570514441229</v>
       </c>
       <c r="W55">
-        <v>0.1929323980750587</v>
+        <v>0.193078094407002</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3134502758940775</v>
+        <v>0.3076456411552984</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1732328460617226</v>
+        <v>0.1747828460617226</v>
       </c>
       <c r="C56">
-        <v>-6879.062799374966</v>
+        <v>-7529.962030777944</v>
       </c>
       <c r="D56">
-        <v>16995.63120062503</v>
+        <v>16791.39296922206</v>
       </c>
       <c r="E56">
-        <v>18921.694</v>
+        <v>19368.355</v>
       </c>
       <c r="F56">
-        <v>24119.694</v>
+        <v>24566.355</v>
       </c>
       <c r="G56">
         <v>245</v>
@@ -5885,37 +5885,37 @@
         <v>1490</v>
       </c>
       <c r="M56">
-        <v>4843.2345552</v>
+        <v>4932.924084</v>
       </c>
       <c r="N56">
-        <v>-3353.2345552</v>
+        <v>-3442.924084</v>
       </c>
       <c r="O56">
-        <v>-419.1543194</v>
+        <v>-430.3655105</v>
       </c>
       <c r="P56">
-        <v>-2934.0802358</v>
+        <v>-3012.5585735</v>
       </c>
       <c r="Q56">
-        <v>-2220.0802358</v>
+        <v>-2298.5585735</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1499362501781338</v>
+        <v>0.1522503890709812</v>
       </c>
       <c r="T56">
-        <v>2.029809344672354</v>
+        <v>2.074916218998407</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.03845570514441229</v>
+        <v>0.03775651050542297</v>
       </c>
       <c r="W56">
-        <v>0.193078094407002</v>
+        <v>0.1932184926905111</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3076456411552984</v>
+        <v>0.3020520840433838</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1747828460617226</v>
+        <v>0.1763328460617226</v>
       </c>
       <c r="C57">
-        <v>-7529.962030777944</v>
+        <v>-8176.010846852896</v>
       </c>
       <c r="D57">
-        <v>16791.39296922206</v>
+        <v>16592.00515314711</v>
       </c>
       <c r="E57">
-        <v>19368.355</v>
+        <v>19815.016</v>
       </c>
       <c r="F57">
-        <v>24566.355</v>
+        <v>25013.016</v>
       </c>
       <c r="G57">
         <v>245</v>
@@ -5967,37 +5967,37 @@
         <v>1490</v>
       </c>
       <c r="M57">
-        <v>4932.924084</v>
+        <v>5022.613612800001</v>
       </c>
       <c r="N57">
-        <v>-3442.924084</v>
+        <v>-3532.613612800001</v>
       </c>
       <c r="O57">
-        <v>-430.3655105</v>
+        <v>-441.5767016000001</v>
       </c>
       <c r="P57">
-        <v>-3012.5585735</v>
+        <v>-3091.036911200001</v>
       </c>
       <c r="Q57">
-        <v>-2298.5585735</v>
+        <v>-2377.036911200001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1522503890709812</v>
+        <v>0.1546697160953216</v>
       </c>
       <c r="T57">
-        <v>2.074916218998407</v>
+        <v>2.122073405793824</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.03775651050542297</v>
+        <v>0.03708228710354042</v>
       </c>
       <c r="W57">
-        <v>0.1932184926905111</v>
+        <v>0.1933538767496091</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3020520840433838</v>
+        <v>0.2966582968283233</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1763328460617226</v>
+        <v>0.1778828460617226</v>
       </c>
       <c r="C58">
-        <v>-8176.010846852896</v>
+        <v>-8817.380007330903</v>
       </c>
       <c r="D58">
-        <v>16592.00515314711</v>
+        <v>16397.2969926691</v>
       </c>
       <c r="E58">
-        <v>19815.016</v>
+        <v>20261.677</v>
       </c>
       <c r="F58">
-        <v>25013.016</v>
+        <v>25459.677</v>
       </c>
       <c r="G58">
         <v>245</v>
@@ -6049,37 +6049,37 @@
         <v>1490</v>
       </c>
       <c r="M58">
-        <v>5022.613612800001</v>
+        <v>5112.303141600001</v>
       </c>
       <c r="N58">
-        <v>-3532.613612800001</v>
+        <v>-3622.303141600001</v>
       </c>
       <c r="O58">
-        <v>-441.5767016000001</v>
+        <v>-452.7878927000002</v>
       </c>
       <c r="P58">
-        <v>-3091.036911200001</v>
+        <v>-3169.515248900001</v>
       </c>
       <c r="Q58">
-        <v>-2377.036911200001</v>
+        <v>-2455.515248900001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1546697160953216</v>
+        <v>0.1572015699580035</v>
       </c>
       <c r="T58">
-        <v>2.122073405793824</v>
+        <v>2.171423950114611</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.03708228710354042</v>
+        <v>0.03643172066312742</v>
       </c>
       <c r="W58">
-        <v>0.1933538767496091</v>
+        <v>0.193484510490844</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2966582968283233</v>
+        <v>0.2914537653050194</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1778828460617226</v>
+        <v>0.1794328460617226</v>
       </c>
       <c r="C59">
-        <v>-8817.380007330903</v>
+        <v>-9454.232349412312</v>
       </c>
       <c r="D59">
-        <v>16397.2969926691</v>
+        <v>16207.10565058769</v>
       </c>
       <c r="E59">
-        <v>20261.677</v>
+        <v>20708.338</v>
       </c>
       <c r="F59">
-        <v>25459.677</v>
+        <v>25906.338</v>
       </c>
       <c r="G59">
         <v>245</v>
@@ -6131,37 +6131,37 @@
         <v>1490</v>
       </c>
       <c r="M59">
-        <v>5112.303141600001</v>
+        <v>5201.992670400001</v>
       </c>
       <c r="N59">
-        <v>-3622.303141600001</v>
+        <v>-3711.992670400001</v>
       </c>
       <c r="O59">
-        <v>-452.7878927000002</v>
+        <v>-463.9990838000001</v>
       </c>
       <c r="P59">
-        <v>-3169.515248900001</v>
+        <v>-3247.993586600001</v>
       </c>
       <c r="Q59">
-        <v>-2455.515248900001</v>
+        <v>-2533.993586600001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1572015699580035</v>
+        <v>0.159853988290337</v>
       </c>
       <c r="T59">
-        <v>2.171423950114611</v>
+        <v>2.223124520355436</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.03643172066312742</v>
+        <v>0.03580358754824592</v>
       </c>
       <c r="W59">
-        <v>0.193484510490844</v>
+        <v>0.1936106396203122</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2914537653050194</v>
+        <v>0.2864287003859673</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1794328460617226</v>
+        <v>0.1809828460617226</v>
       </c>
       <c r="C60">
-        <v>-9454.232349412301</v>
+        <v>-10086.72324196347</v>
       </c>
       <c r="D60">
-        <v>16207.10565058769</v>
+        <v>16021.27575803653</v>
       </c>
       <c r="E60">
-        <v>20708.338</v>
+        <v>21154.999</v>
       </c>
       <c r="F60">
-        <v>25906.338</v>
+        <v>26352.999</v>
       </c>
       <c r="G60">
         <v>245</v>
@@ -6213,37 +6213,37 @@
         <v>1490</v>
       </c>
       <c r="M60">
-        <v>5201.992670399999</v>
+        <v>5291.6821992</v>
       </c>
       <c r="N60">
-        <v>-3711.992670399999</v>
+        <v>-3801.6821992</v>
       </c>
       <c r="O60">
-        <v>-463.9990837999999</v>
+        <v>-475.2102748999999</v>
       </c>
       <c r="P60">
-        <v>-3247.993586599999</v>
+        <v>-3326.4719243</v>
       </c>
       <c r="Q60">
-        <v>-2533.993586599999</v>
+        <v>-2612.4719243</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1598539882903369</v>
+        <v>0.1626357928827842</v>
       </c>
       <c r="T60">
-        <v>2.223124520355435</v>
+        <v>2.277347069632397</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.03580358754824593</v>
+        <v>0.0351967470813265</v>
       </c>
       <c r="W60">
-        <v>0.1936106396203122</v>
+        <v>0.1937324931860696</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2864287003859675</v>
+        <v>0.281573976650612</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1809828460617226</v>
+        <v>0.1825328460617226</v>
       </c>
       <c r="C61">
-        <v>-10086.72324196347</v>
+        <v>-10715.00100882099</v>
       </c>
       <c r="D61">
-        <v>16021.27575803653</v>
+        <v>15839.65899117901</v>
       </c>
       <c r="E61">
-        <v>21154.999</v>
+        <v>21601.66</v>
       </c>
       <c r="F61">
-        <v>26352.999</v>
+        <v>26799.66</v>
       </c>
       <c r="G61">
         <v>245</v>
@@ -6295,37 +6295,37 @@
         <v>1490</v>
       </c>
       <c r="M61">
-        <v>5291.6821992</v>
+        <v>5381.371728</v>
       </c>
       <c r="N61">
-        <v>-3801.6821992</v>
+        <v>-3891.371728</v>
       </c>
       <c r="O61">
-        <v>-475.2102748999999</v>
+        <v>-486.421466</v>
       </c>
       <c r="P61">
-        <v>-3326.4719243</v>
+        <v>-3404.950262</v>
       </c>
       <c r="Q61">
-        <v>-2612.4719243</v>
+        <v>-2690.950262</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1626357928827842</v>
+        <v>0.1655566877048538</v>
       </c>
       <c r="T61">
-        <v>2.277347069632397</v>
+        <v>2.334280746373206</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.0351967470813265</v>
+        <v>0.03461013462997106</v>
       </c>
       <c r="W61">
-        <v>0.1937324931860696</v>
+        <v>0.1938502849663018</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.281573976650612</v>
+        <v>0.2768810770397685</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1825328460617226</v>
+        <v>0.1840828460617226</v>
       </c>
       <c r="C62">
-        <v>-10715.00100882099</v>
+        <v>-11339.2073236272</v>
       </c>
       <c r="D62">
-        <v>15839.65899117901</v>
+        <v>15662.1136763728</v>
       </c>
       <c r="E62">
-        <v>21601.66</v>
+        <v>22048.321</v>
       </c>
       <c r="F62">
-        <v>26799.66</v>
+        <v>27246.321</v>
       </c>
       <c r="G62">
         <v>245</v>
@@ -6377,37 +6377,37 @@
         <v>1490</v>
       </c>
       <c r="M62">
-        <v>5381.371728</v>
+        <v>5471.061256800001</v>
       </c>
       <c r="N62">
-        <v>-3891.371728</v>
+        <v>-3981.061256800001</v>
       </c>
       <c r="O62">
-        <v>-486.421466</v>
+        <v>-497.6326571000001</v>
       </c>
       <c r="P62">
-        <v>-3404.950262</v>
+        <v>-3483.428599700001</v>
       </c>
       <c r="Q62">
-        <v>-2690.950262</v>
+        <v>-2769.428599700001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1655566877048538</v>
+        <v>0.1686273720049783</v>
       </c>
       <c r="T62">
-        <v>2.334280746373206</v>
+        <v>2.394134098844315</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.03461013462997106</v>
+        <v>0.03404275537374202</v>
       </c>
       <c r="W62">
-        <v>0.1938502849663018</v>
+        <v>0.1939642147209526</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2768810770397685</v>
+        <v>0.2723420429899361</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1840828460617226</v>
+        <v>0.1856328460617226</v>
       </c>
       <c r="C63">
-        <v>-11339.2073236272</v>
+        <v>-11959.47757840603</v>
       </c>
       <c r="D63">
-        <v>15662.1136763728</v>
+        <v>15488.50442159397</v>
       </c>
       <c r="E63">
-        <v>22048.321</v>
+        <v>22494.982</v>
       </c>
       <c r="F63">
-        <v>27246.321</v>
+        <v>27692.982</v>
       </c>
       <c r="G63">
         <v>245</v>
@@ -6459,37 +6459,37 @@
         <v>1490</v>
       </c>
       <c r="M63">
-        <v>5471.061256800001</v>
+        <v>5560.7507856</v>
       </c>
       <c r="N63">
-        <v>-3981.061256800001</v>
+        <v>-4070.7507856</v>
       </c>
       <c r="O63">
-        <v>-497.6326571000001</v>
+        <v>-508.8438482</v>
       </c>
       <c r="P63">
-        <v>-3483.428599700001</v>
+        <v>-3561.9069374</v>
       </c>
       <c r="Q63">
-        <v>-2769.428599700001</v>
+        <v>-2847.9069374</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1686273720049783</v>
+        <v>0.1718596712682672</v>
       </c>
       <c r="T63">
-        <v>2.394134098844315</v>
+        <v>2.45713762776127</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.03404275537374202</v>
+        <v>0.03349367867416554</v>
       </c>
       <c r="W63">
-        <v>0.1939642147209526</v>
+        <v>0.1940744693222276</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2723420429899361</v>
+        <v>0.2679494293933243</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1856328460617226</v>
+        <v>0.1871828460617226</v>
       </c>
       <c r="C64">
-        <v>-11959.47757840603</v>
+        <v>-12575.94122789428</v>
       </c>
       <c r="D64">
-        <v>15488.50442159397</v>
+        <v>15318.70177210572</v>
       </c>
       <c r="E64">
-        <v>22494.982</v>
+        <v>22941.643</v>
       </c>
       <c r="F64">
-        <v>27692.982</v>
+        <v>28139.643</v>
       </c>
       <c r="G64">
         <v>245</v>
@@ -6541,37 +6541,37 @@
         <v>1490</v>
       </c>
       <c r="M64">
-        <v>5560.7507856</v>
+        <v>5650.4403144</v>
       </c>
       <c r="N64">
-        <v>-4070.7507856</v>
+        <v>-4160.4403144</v>
       </c>
       <c r="O64">
-        <v>-508.8438482</v>
+        <v>-520.0550393</v>
       </c>
       <c r="P64">
-        <v>-3561.9069374</v>
+        <v>-3640.3852751</v>
       </c>
       <c r="Q64">
-        <v>-2847.9069374</v>
+        <v>-2926.3852751</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1718596712682672</v>
+        <v>0.1752666894106527</v>
       </c>
       <c r="T64">
-        <v>2.45713762776127</v>
+        <v>2.523546752835899</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.03349367867416554</v>
+        <v>0.03296203298092482</v>
       </c>
       <c r="W64">
-        <v>0.1940744693222276</v>
+        <v>0.1941812237774303</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2679494293933243</v>
+        <v>0.2636962638473985</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1871828460617226</v>
+        <v>0.1887328460617226</v>
       </c>
       <c r="C65">
-        <v>-12575.94122789428</v>
+        <v>-13188.72211146891</v>
       </c>
       <c r="D65">
-        <v>15318.70177210572</v>
+        <v>15152.58188853109</v>
       </c>
       <c r="E65">
-        <v>22941.643</v>
+        <v>23388.304</v>
       </c>
       <c r="F65">
-        <v>28139.643</v>
+        <v>28586.304</v>
       </c>
       <c r="G65">
         <v>245</v>
@@ -6623,37 +6623,37 @@
         <v>1490</v>
       </c>
       <c r="M65">
-        <v>5650.4403144</v>
+        <v>5740.1298432</v>
       </c>
       <c r="N65">
-        <v>-4160.4403144</v>
+        <v>-4250.1298432</v>
       </c>
       <c r="O65">
-        <v>-520.0550393</v>
+        <v>-531.2662304</v>
       </c>
       <c r="P65">
-        <v>-3640.3852751</v>
+        <v>-3718.8636128</v>
       </c>
       <c r="Q65">
-        <v>-2926.3852751</v>
+        <v>-3004.8636128</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1752666894106527</v>
+        <v>0.1788629863387264</v>
       </c>
       <c r="T65">
-        <v>2.523546752835899</v>
+        <v>2.593645273748007</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.03296203298092482</v>
+        <v>0.03244700121559787</v>
       </c>
       <c r="W65">
-        <v>0.1941812237774303</v>
+        <v>0.194284642155908</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2636962638473985</v>
+        <v>0.2595760097247829</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1887328460617226</v>
+        <v>0.1902828460617226</v>
       </c>
       <c r="C66">
-        <v>-13188.72211146891</v>
+        <v>-13797.93875435257</v>
       </c>
       <c r="D66">
-        <v>15152.58188853109</v>
+        <v>14990.02624564743</v>
       </c>
       <c r="E66">
-        <v>23388.304</v>
+        <v>23834.965</v>
       </c>
       <c r="F66">
-        <v>28586.304</v>
+        <v>29032.965</v>
       </c>
       <c r="G66">
         <v>245</v>
@@ -6705,37 +6705,37 @@
         <v>1490</v>
       </c>
       <c r="M66">
-        <v>5740.1298432</v>
+        <v>5829.819372</v>
       </c>
       <c r="N66">
-        <v>-4250.1298432</v>
+        <v>-4339.819372</v>
       </c>
       <c r="O66">
-        <v>-531.2662304</v>
+        <v>-542.4774215</v>
       </c>
       <c r="P66">
-        <v>-3718.8636128</v>
+        <v>-3797.3419505</v>
       </c>
       <c r="Q66">
-        <v>-3004.8636128</v>
+        <v>-3083.3419505</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1788629863387264</v>
+        <v>0.1826647859484044</v>
       </c>
       <c r="T66">
-        <v>2.593645273748007</v>
+        <v>2.667749424426523</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.03244700121559787</v>
+        <v>0.03194781658151175</v>
       </c>
       <c r="W66">
-        <v>0.194284642155908</v>
+        <v>0.1943848784304325</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2595760097247829</v>
+        <v>0.255582532652094</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1902828460617226</v>
+        <v>0.1918328460617226</v>
       </c>
       <c r="C67">
-        <v>-13797.93875435257</v>
+        <v>-14403.7046496371</v>
       </c>
       <c r="D67">
-        <v>14990.02624564743</v>
+        <v>14830.9213503629</v>
       </c>
       <c r="E67">
-        <v>23834.965</v>
+        <v>24281.626</v>
       </c>
       <c r="F67">
-        <v>29032.965</v>
+        <v>29479.626</v>
       </c>
       <c r="G67">
         <v>245</v>
@@ -6787,37 +6787,37 @@
         <v>1490</v>
       </c>
       <c r="M67">
-        <v>5829.819372</v>
+        <v>5919.5089008</v>
       </c>
       <c r="N67">
-        <v>-4339.819372</v>
+        <v>-4429.5089008</v>
       </c>
       <c r="O67">
-        <v>-542.4774215</v>
+        <v>-553.6886126000001</v>
       </c>
       <c r="P67">
-        <v>-3797.3419505</v>
+        <v>-3875.820288200001</v>
       </c>
       <c r="Q67">
-        <v>-3083.3419505</v>
+        <v>-3161.820288200001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1826647859484044</v>
+        <v>0.1866902208292398</v>
       </c>
       <c r="T67">
-        <v>2.667749424426523</v>
+        <v>2.746212642792008</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.03194781658151175</v>
+        <v>0.03146375875451914</v>
       </c>
       <c r="W67">
-        <v>0.1943848784304325</v>
+        <v>0.1944820772420926</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.255582532652094</v>
+        <v>0.2517100700361531</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1918328460617226</v>
+        <v>0.1933828460617226</v>
       </c>
       <c r="C68">
-        <v>-14403.7046496371</v>
+        <v>-15006.12852253528</v>
       </c>
       <c r="D68">
-        <v>14830.9213503629</v>
+        <v>14675.15847746472</v>
       </c>
       <c r="E68">
-        <v>24281.626</v>
+        <v>24728.287</v>
       </c>
       <c r="F68">
-        <v>29479.626</v>
+        <v>29926.287</v>
       </c>
       <c r="G68">
         <v>245</v>
@@ -6869,37 +6869,37 @@
         <v>1490</v>
       </c>
       <c r="M68">
-        <v>5919.5089008</v>
+        <v>6009.1984296</v>
       </c>
       <c r="N68">
-        <v>-4429.5089008</v>
+        <v>-4519.1984296</v>
       </c>
       <c r="O68">
-        <v>-553.6886126000001</v>
+        <v>-564.8998037</v>
       </c>
       <c r="P68">
-        <v>-3875.820288200001</v>
+        <v>-3954.2986259</v>
       </c>
       <c r="Q68">
-        <v>-3161.820288200001</v>
+        <v>-3240.2986259</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1866902208292398</v>
+        <v>0.1909596214604289</v>
       </c>
       <c r="T68">
-        <v>2.746212642792008</v>
+        <v>2.829431207725099</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.03146375875451914</v>
+        <v>0.03099415041489946</v>
       </c>
       <c r="W68">
-        <v>0.1944820772420926</v>
+        <v>0.1945763745966882</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2517100700361531</v>
+        <v>0.2479532033191957</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1933828460617226</v>
+        <v>0.1949328460617226</v>
       </c>
       <c r="C69">
-        <v>-15006.12852253528</v>
+        <v>-15605.31457815351</v>
       </c>
       <c r="D69">
-        <v>14675.15847746472</v>
+        <v>14522.63342184649</v>
       </c>
       <c r="E69">
-        <v>24728.287</v>
+        <v>25174.948</v>
       </c>
       <c r="F69">
-        <v>29926.287</v>
+        <v>30372.948</v>
       </c>
       <c r="G69">
         <v>245</v>
@@ -6951,37 +6951,37 @@
         <v>1490</v>
       </c>
       <c r="M69">
-        <v>6009.1984296</v>
+        <v>6098.887958400001</v>
       </c>
       <c r="N69">
-        <v>-4519.1984296</v>
+        <v>-4608.887958400001</v>
       </c>
       <c r="O69">
-        <v>-564.8998037</v>
+        <v>-576.1109948000001</v>
       </c>
       <c r="P69">
-        <v>-3954.2986259</v>
+        <v>-4032.7769636</v>
       </c>
       <c r="Q69">
-        <v>-3240.2986259</v>
+        <v>-3318.7769636</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1909596214604289</v>
+        <v>0.1954958596310672</v>
       </c>
       <c r="T69">
-        <v>2.829431207725099</v>
+        <v>2.917850932966509</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.03099415041489946</v>
+        <v>0.03053835408526858</v>
       </c>
       <c r="W69">
-        <v>0.1945763745966882</v>
+        <v>0.1946678984996781</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2479532033191957</v>
+        <v>0.2443068326821486</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1949328460617226</v>
+        <v>0.1964828460617226</v>
       </c>
       <c r="C70">
-        <v>-15605.31457815351</v>
+        <v>-16201.36273397244</v>
       </c>
       <c r="D70">
-        <v>14522.63342184649</v>
+        <v>14373.24626602756</v>
       </c>
       <c r="E70">
-        <v>25174.948</v>
+        <v>25621.609</v>
       </c>
       <c r="F70">
-        <v>30372.948</v>
+        <v>30819.609</v>
       </c>
       <c r="G70">
         <v>245</v>
@@ -7033,37 +7033,37 @@
         <v>1490</v>
       </c>
       <c r="M70">
-        <v>6098.887958400001</v>
+        <v>6188.5774872</v>
       </c>
       <c r="N70">
-        <v>-4608.887958400001</v>
+        <v>-4698.5774872</v>
       </c>
       <c r="O70">
-        <v>-576.1109948000001</v>
+        <v>-587.3221859</v>
       </c>
       <c r="P70">
-        <v>-4032.7769636</v>
+        <v>-4111.2553013</v>
       </c>
       <c r="Q70">
-        <v>-3318.7769636</v>
+        <v>-3397.2553013</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1954958596310672</v>
+        <v>0.2003247583288436</v>
       </c>
       <c r="T70">
-        <v>2.917850932966509</v>
+        <v>3.01197515661059</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.03053835408526858</v>
+        <v>0.0300957692434531</v>
       </c>
       <c r="W70">
-        <v>0.1946678984996781</v>
+        <v>0.1947567695359146</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2443068326821486</v>
+        <v>0.2407661539476248</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1964828460617226</v>
+        <v>0.1980328460617226</v>
       </c>
       <c r="C71">
-        <v>-16201.36273397244</v>
+        <v>-16794.368838125</v>
       </c>
       <c r="D71">
-        <v>14373.24626602756</v>
+        <v>14226.901161875</v>
       </c>
       <c r="E71">
-        <v>25621.609</v>
+        <v>26068.27</v>
       </c>
       <c r="F71">
-        <v>30819.609</v>
+        <v>31266.27</v>
       </c>
       <c r="G71">
         <v>245</v>
@@ -7115,37 +7115,37 @@
         <v>1490</v>
       </c>
       <c r="M71">
-        <v>6188.5774872</v>
+        <v>6278.267016000001</v>
       </c>
       <c r="N71">
-        <v>-4698.5774872</v>
+        <v>-4788.267016000001</v>
       </c>
       <c r="O71">
-        <v>-587.3221859</v>
+        <v>-598.5333770000001</v>
       </c>
       <c r="P71">
-        <v>-4111.2553013</v>
+        <v>-4189.733639000001</v>
       </c>
       <c r="Q71">
-        <v>-3397.2553013</v>
+        <v>-3475.733639000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2003247583288436</v>
+        <v>0.2054755836064717</v>
       </c>
       <c r="T71">
-        <v>3.01197515661059</v>
+        <v>3.112374328497609</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.0300957692434531</v>
+        <v>0.02966582968283233</v>
       </c>
       <c r="W71">
-        <v>0.1947567695359146</v>
+        <v>0.1948431013996873</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2407661539476248</v>
+        <v>0.2373266374626587</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1980328460617226</v>
+        <v>0.1995828460617226</v>
       </c>
       <c r="C72">
-        <v>-16794.368838125</v>
+        <v>-17384.42487447421</v>
       </c>
       <c r="D72">
-        <v>14226.901161875</v>
+        <v>14083.50612552579</v>
       </c>
       <c r="E72">
-        <v>26068.27</v>
+        <v>26514.931</v>
       </c>
       <c r="F72">
-        <v>31266.27</v>
+        <v>31712.931</v>
       </c>
       <c r="G72">
         <v>245</v>
@@ -7197,37 +7197,37 @@
         <v>1490</v>
       </c>
       <c r="M72">
-        <v>6278.267016000001</v>
+        <v>6367.956544800001</v>
       </c>
       <c r="N72">
-        <v>-4788.267016000001</v>
+        <v>-4877.956544800001</v>
       </c>
       <c r="O72">
-        <v>-598.5333770000001</v>
+        <v>-609.7445681000002</v>
       </c>
       <c r="P72">
-        <v>-4189.733639000001</v>
+        <v>-4268.211976700001</v>
       </c>
       <c r="Q72">
-        <v>-3475.733639000001</v>
+        <v>-3554.211976700001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2054755836064717</v>
+        <v>0.2109816382135915</v>
       </c>
       <c r="T72">
-        <v>3.112374328497609</v>
+        <v>3.219697581204424</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.02966582968283233</v>
+        <v>0.02924800109575018</v>
       </c>
       <c r="W72">
-        <v>0.1948431013996873</v>
+        <v>0.1949270013799734</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2373266374626587</v>
+        <v>0.2339840087660015</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1995828460617226</v>
+        <v>0.2011328460617226</v>
       </c>
       <c r="C73">
-        <v>-17384.42487447421</v>
+        <v>-17971.61915541268</v>
       </c>
       <c r="D73">
-        <v>14083.50612552579</v>
+        <v>13942.97284458732</v>
       </c>
       <c r="E73">
-        <v>26514.931</v>
+        <v>26961.592</v>
       </c>
       <c r="F73">
-        <v>31712.931</v>
+        <v>32159.592</v>
       </c>
       <c r="G73">
         <v>245</v>
@@ -7279,37 +7279,37 @@
         <v>1490</v>
       </c>
       <c r="M73">
-        <v>6367.956544799999</v>
+        <v>6457.6460736</v>
       </c>
       <c r="N73">
-        <v>-4877.956544799999</v>
+        <v>-4967.6460736</v>
       </c>
       <c r="O73">
-        <v>-609.7445680999999</v>
+        <v>-620.9557592</v>
       </c>
       <c r="P73">
-        <v>-4268.211976699999</v>
+        <v>-4346.6903144</v>
       </c>
       <c r="Q73">
-        <v>-3554.211976699999</v>
+        <v>-3632.6903144</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2109816382135914</v>
+        <v>0.2168809824355054</v>
       </c>
       <c r="T73">
-        <v>3.219697581204423</v>
+        <v>3.334686780533152</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.0292480010957502</v>
+        <v>0.02884177885830922</v>
       </c>
       <c r="W73">
-        <v>0.1949270013799734</v>
+        <v>0.1950085708052515</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2339840087660016</v>
+        <v>0.2307342308664737</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2011328460617226</v>
+        <v>0.2026828460617226</v>
       </c>
       <c r="C74">
-        <v>-17971.61915541268</v>
+        <v>-18556.03650323294</v>
       </c>
       <c r="D74">
-        <v>13942.97284458732</v>
+        <v>13805.21649676706</v>
       </c>
       <c r="E74">
-        <v>26961.592</v>
+        <v>27408.253</v>
       </c>
       <c r="F74">
-        <v>32159.592</v>
+        <v>32606.253</v>
       </c>
       <c r="G74">
         <v>245</v>
@@ -7361,37 +7361,37 @@
         <v>1490</v>
       </c>
       <c r="M74">
-        <v>6457.6460736</v>
+        <v>6547.3356024</v>
       </c>
       <c r="N74">
-        <v>-4967.6460736</v>
+        <v>-5057.3356024</v>
       </c>
       <c r="O74">
-        <v>-620.9557592</v>
+        <v>-632.1669502999999</v>
       </c>
       <c r="P74">
-        <v>-4346.6903144</v>
+        <v>-4425.168652099999</v>
       </c>
       <c r="Q74">
-        <v>-3632.6903144</v>
+        <v>-3711.168652099999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2168809824355054</v>
+        <v>0.2232173151183019</v>
       </c>
       <c r="T74">
-        <v>3.334686780533152</v>
+        <v>3.458193698330676</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.02884177885830922</v>
+        <v>0.02844668599723649</v>
       </c>
       <c r="W74">
-        <v>0.1950085708052515</v>
+        <v>0.1950879054517549</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2307342308664737</v>
+        <v>0.2275734879778919</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2026828460617226</v>
+        <v>0.2042328460617226</v>
       </c>
       <c r="C75">
-        <v>-18556.03650323294</v>
+        <v>-19137.75842085133</v>
       </c>
       <c r="D75">
-        <v>13805.21649676706</v>
+        <v>13670.15557914867</v>
       </c>
       <c r="E75">
-        <v>27408.253</v>
+        <v>27854.914</v>
       </c>
       <c r="F75">
-        <v>32606.253</v>
+        <v>33052.914</v>
       </c>
       <c r="G75">
         <v>245</v>
@@ -7443,37 +7443,37 @@
         <v>1490</v>
       </c>
       <c r="M75">
-        <v>6547.3356024</v>
+        <v>6637.0251312</v>
       </c>
       <c r="N75">
-        <v>-5057.3356024</v>
+        <v>-5147.0251312</v>
       </c>
       <c r="O75">
-        <v>-632.1669502999999</v>
+        <v>-643.3781414</v>
       </c>
       <c r="P75">
-        <v>-4425.168652099999</v>
+        <v>-4503.6469898</v>
       </c>
       <c r="Q75">
-        <v>-3711.168652099999</v>
+        <v>-3789.6469898</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2232173151183019</v>
+        <v>0.2300410580074674</v>
       </c>
       <c r="T75">
-        <v>3.458193698330676</v>
+        <v>3.591201148266472</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.02844668599723649</v>
+        <v>0.02806227132159816</v>
       </c>
       <c r="W75">
-        <v>0.1950879054517549</v>
+        <v>0.1951650959186231</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2275734879778919</v>
+        <v>0.2244981705727852</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2042328460617226</v>
+        <v>0.2057828460617226</v>
       </c>
       <c r="C76">
-        <v>-19137.75842085133</v>
+        <v>-19716.86325260755</v>
       </c>
       <c r="D76">
-        <v>13670.15557914867</v>
+        <v>13537.71174739245</v>
       </c>
       <c r="E76">
-        <v>27854.914</v>
+        <v>28301.575</v>
       </c>
       <c r="F76">
-        <v>33052.914</v>
+        <v>33499.575</v>
       </c>
       <c r="G76">
         <v>245</v>
@@ -7525,37 +7525,37 @@
         <v>1490</v>
       </c>
       <c r="M76">
-        <v>6637.0251312</v>
+        <v>6726.71466</v>
       </c>
       <c r="N76">
-        <v>-5147.0251312</v>
+        <v>-5236.71466</v>
       </c>
       <c r="O76">
-        <v>-643.3781414</v>
+        <v>-654.5893325</v>
       </c>
       <c r="P76">
-        <v>-4503.6469898</v>
+        <v>-4582.1253275</v>
       </c>
       <c r="Q76">
-        <v>-3789.6469898</v>
+        <v>-3868.1253275</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2300410580074674</v>
+        <v>0.2374107003277661</v>
       </c>
       <c r="T76">
-        <v>3.591201148266472</v>
+        <v>3.73484919419713</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.02806227132159816</v>
+        <v>0.02768810770397685</v>
       </c>
       <c r="W76">
-        <v>0.1951650959186231</v>
+        <v>0.1952402279730414</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2244981705727852</v>
+        <v>0.2215048616318148</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2057828460617226</v>
+        <v>0.2073328460617226</v>
       </c>
       <c r="C77">
-        <v>-19716.86325260755</v>
+        <v>-20293.42633580641</v>
       </c>
       <c r="D77">
-        <v>13537.71174739245</v>
+        <v>13407.80966419359</v>
       </c>
       <c r="E77">
-        <v>28301.575</v>
+        <v>28748.236</v>
       </c>
       <c r="F77">
-        <v>33499.575</v>
+        <v>33946.236</v>
       </c>
       <c r="G77">
         <v>245</v>
@@ -7607,37 +7607,37 @@
         <v>1490</v>
       </c>
       <c r="M77">
-        <v>6726.71466</v>
+        <v>6816.404188799999</v>
       </c>
       <c r="N77">
-        <v>-5236.71466</v>
+        <v>-5326.404188799999</v>
       </c>
       <c r="O77">
-        <v>-654.5893325</v>
+        <v>-665.8005235999999</v>
       </c>
       <c r="P77">
-        <v>-4582.1253275</v>
+        <v>-4660.603665199999</v>
       </c>
       <c r="Q77">
-        <v>-3868.1253275</v>
+        <v>-3946.603665199999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2374107003277661</v>
+        <v>0.2453944795080897</v>
       </c>
       <c r="T77">
-        <v>3.73484919419713</v>
+        <v>3.890467910622012</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.02768810770397685</v>
+        <v>0.02732379049734558</v>
       </c>
       <c r="W77">
-        <v>0.1952402279730414</v>
+        <v>0.195313382868133</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2215048616318148</v>
+        <v>0.2185903239787647</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2073328460617226</v>
+        <v>0.2088828460617226</v>
       </c>
       <c r="C78">
-        <v>-20293.42633580641</v>
+        <v>-20867.52014361768</v>
       </c>
       <c r="D78">
-        <v>13407.80966419359</v>
+        <v>13280.37685638231</v>
       </c>
       <c r="E78">
-        <v>28748.236</v>
+        <v>29194.897</v>
       </c>
       <c r="F78">
-        <v>33946.236</v>
+        <v>34392.897</v>
       </c>
       <c r="G78">
         <v>245</v>
@@ -7689,37 +7689,37 @@
         <v>1490</v>
       </c>
       <c r="M78">
-        <v>6816.404188799999</v>
+        <v>6906.0937176</v>
       </c>
       <c r="N78">
-        <v>-5326.404188799999</v>
+        <v>-5416.0937176</v>
       </c>
       <c r="O78">
-        <v>-665.8005235999999</v>
+        <v>-677.0117147</v>
       </c>
       <c r="P78">
-        <v>-4660.603665199999</v>
+        <v>-4739.0820029</v>
       </c>
       <c r="Q78">
-        <v>-3946.603665199999</v>
+        <v>-4025.0820029</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2453944795080897</v>
+        <v>0.2540725003562675</v>
       </c>
       <c r="T78">
-        <v>3.890467910622012</v>
+        <v>4.059618689344708</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.02732379049734558</v>
+        <v>0.02696893607530212</v>
       </c>
       <c r="W78">
-        <v>0.195313382868133</v>
+        <v>0.1953846376360793</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2185903239787647</v>
+        <v>0.215751488602417</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2088828460617226</v>
+        <v>0.2104328460617226</v>
       </c>
       <c r="C79">
-        <v>-20867.52014361768</v>
+        <v>-21439.21441990372</v>
       </c>
       <c r="D79">
-        <v>13280.37685638231</v>
+        <v>13155.34358009627</v>
       </c>
       <c r="E79">
-        <v>29194.897</v>
+        <v>29641.558</v>
       </c>
       <c r="F79">
-        <v>34392.897</v>
+        <v>34839.558</v>
       </c>
       <c r="G79">
         <v>245</v>
@@ -7771,37 +7771,37 @@
         <v>1490</v>
       </c>
       <c r="M79">
-        <v>6906.0937176</v>
+        <v>6995.783246399999</v>
       </c>
       <c r="N79">
-        <v>-5416.0937176</v>
+        <v>-5505.783246399999</v>
       </c>
       <c r="O79">
-        <v>-677.0117147</v>
+        <v>-688.2229057999999</v>
       </c>
       <c r="P79">
-        <v>-4739.0820029</v>
+        <v>-4817.560340599999</v>
       </c>
       <c r="Q79">
-        <v>-4025.0820029</v>
+        <v>-4103.560340599999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2540725003562675</v>
+        <v>0.2635394321906433</v>
       </c>
       <c r="T79">
-        <v>4.059618689344708</v>
+        <v>4.244146811587649</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.02696893607530212</v>
+        <v>0.02662318048459313</v>
       </c>
       <c r="W79">
-        <v>0.1953846376360793</v>
+        <v>0.1954540653586937</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.215751488602417</v>
+        <v>0.212985443876745</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2104328460617226</v>
+        <v>0.2119828460617226</v>
       </c>
       <c r="C80">
-        <v>-21439.21441990372</v>
+        <v>-22008.57630650171</v>
       </c>
       <c r="D80">
-        <v>13155.34358009627</v>
+        <v>13032.64269349829</v>
       </c>
       <c r="E80">
-        <v>29641.558</v>
+        <v>30088.219</v>
       </c>
       <c r="F80">
-        <v>34839.558</v>
+        <v>35286.219</v>
       </c>
       <c r="G80">
         <v>245</v>
@@ -7853,37 +7853,37 @@
         <v>1490</v>
       </c>
       <c r="M80">
-        <v>6995.783246399999</v>
+        <v>7085.4727752</v>
       </c>
       <c r="N80">
-        <v>-5505.783246399999</v>
+        <v>-5595.4727752</v>
       </c>
       <c r="O80">
-        <v>-688.2229057999999</v>
+        <v>-699.4340969</v>
       </c>
       <c r="P80">
-        <v>-4817.560340599999</v>
+        <v>-4896.038678299999</v>
       </c>
       <c r="Q80">
-        <v>-4103.560340599999</v>
+        <v>-4182.038678299999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2635394321906433</v>
+        <v>0.273907976580674</v>
       </c>
       <c r="T80">
-        <v>4.244146811587649</v>
+        <v>4.446249040710871</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.02662318048459313</v>
+        <v>0.02628617819997802</v>
       </c>
       <c r="W80">
-        <v>0.1954540653586937</v>
+        <v>0.1955217354174444</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.212985443876745</v>
+        <v>0.2102894255998241</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2119828460617226</v>
+        <v>0.2135328460617226</v>
       </c>
       <c r="C81">
-        <v>-22008.57630650171</v>
+        <v>-22575.67046344873</v>
       </c>
       <c r="D81">
-        <v>13032.64269349829</v>
+        <v>12912.20953655126</v>
       </c>
       <c r="E81">
-        <v>30088.219</v>
+        <v>30534.88</v>
       </c>
       <c r="F81">
-        <v>35286.219</v>
+        <v>35732.88</v>
       </c>
       <c r="G81">
         <v>245</v>
@@ -7935,37 +7935,37 @@
         <v>1490</v>
       </c>
       <c r="M81">
-        <v>7085.4727752</v>
+        <v>7175.162303999999</v>
       </c>
       <c r="N81">
-        <v>-5595.4727752</v>
+        <v>-5685.162303999999</v>
       </c>
       <c r="O81">
-        <v>-699.4340969</v>
+        <v>-710.6452879999999</v>
       </c>
       <c r="P81">
-        <v>-4896.038678299999</v>
+        <v>-4974.517016</v>
       </c>
       <c r="Q81">
-        <v>-4182.038678299999</v>
+        <v>-4260.517016</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.273907976580674</v>
+        <v>0.2853133754097076</v>
       </c>
       <c r="T81">
-        <v>4.446249040710871</v>
+        <v>4.668561492746415</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.02628617819997802</v>
+        <v>0.0259576009724783</v>
       </c>
       <c r="W81">
-        <v>0.1955217354174444</v>
+        <v>0.1955877137247264</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2102894255998241</v>
+        <v>0.2076608077798263</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2135328460617226</v>
+        <v>0.2150828460617226</v>
       </c>
       <c r="C82">
-        <v>-22575.67046344873</v>
+        <v>-23140.55918260203</v>
       </c>
       <c r="D82">
-        <v>12912.20953655126</v>
+        <v>12793.98181739798</v>
       </c>
       <c r="E82">
-        <v>30534.88</v>
+        <v>30981.541</v>
       </c>
       <c r="F82">
-        <v>35732.88</v>
+        <v>36179.541</v>
       </c>
       <c r="G82">
         <v>245</v>
@@ -8017,37 +8017,37 @@
         <v>1490</v>
       </c>
       <c r="M82">
-        <v>7175.162303999999</v>
+        <v>7264.851832800001</v>
       </c>
       <c r="N82">
-        <v>-5685.162303999999</v>
+        <v>-5774.851832800001</v>
       </c>
       <c r="O82">
-        <v>-710.6452879999999</v>
+        <v>-721.8564791000001</v>
       </c>
       <c r="P82">
-        <v>-4974.517016</v>
+        <v>-5052.995353700001</v>
       </c>
       <c r="Q82">
-        <v>-4260.517016</v>
+        <v>-4338.995353700001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2853133754097076</v>
+        <v>0.2979193425365343</v>
       </c>
       <c r="T82">
-        <v>4.668561492746415</v>
+        <v>4.914275255522542</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.0259576009724783</v>
+        <v>0.02563713676294152</v>
       </c>
       <c r="W82">
-        <v>0.1955877137247264</v>
+        <v>0.1956520629380013</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2076608077798263</v>
+        <v>0.2050970941035322</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2150828460617226</v>
+        <v>0.2166328460617226</v>
       </c>
       <c r="C83">
-        <v>-23140.55918260203</v>
+        <v>-23703.30249507373</v>
       </c>
       <c r="D83">
-        <v>12793.98181739798</v>
+        <v>12677.89950492628</v>
       </c>
       <c r="E83">
-        <v>30981.541</v>
+        <v>31428.202</v>
       </c>
       <c r="F83">
-        <v>36179.541</v>
+        <v>36626.202</v>
       </c>
       <c r="G83">
         <v>245</v>
@@ -8099,37 +8099,37 @@
         <v>1490</v>
       </c>
       <c r="M83">
-        <v>7264.851832800001</v>
+        <v>7354.541361600001</v>
       </c>
       <c r="N83">
-        <v>-5774.851832800001</v>
+        <v>-5864.541361600001</v>
       </c>
       <c r="O83">
-        <v>-721.8564791000001</v>
+        <v>-733.0676702000002</v>
       </c>
       <c r="P83">
-        <v>-5052.995353700001</v>
+        <v>-5131.473691400001</v>
       </c>
       <c r="Q83">
-        <v>-4338.995353700001</v>
+        <v>-4417.473691400001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2979193425365343</v>
+        <v>0.3119259726774529</v>
       </c>
       <c r="T83">
-        <v>4.914275255522542</v>
+        <v>5.187290547496016</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.02563713676294152</v>
+        <v>0.02532448875363736</v>
       </c>
       <c r="W83">
-        <v>0.1956520629380013</v>
+        <v>0.1957148426582696</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2050970941035322</v>
+        <v>0.2025959100290988</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2166328460617226</v>
+        <v>0.2181828460617226</v>
       </c>
       <c r="C84">
-        <v>-23703.30249507373</v>
+        <v>-24263.95827286966</v>
       </c>
       <c r="D84">
-        <v>12677.89950492628</v>
+        <v>12563.90472713035</v>
       </c>
       <c r="E84">
-        <v>31428.202</v>
+        <v>31874.863</v>
       </c>
       <c r="F84">
-        <v>36626.202</v>
+        <v>37072.863</v>
       </c>
       <c r="G84">
         <v>245</v>
@@ -8181,37 +8181,37 @@
         <v>1490</v>
       </c>
       <c r="M84">
-        <v>7354.541361600001</v>
+        <v>7444.230890400001</v>
       </c>
       <c r="N84">
-        <v>-5864.541361600001</v>
+        <v>-5954.230890400001</v>
       </c>
       <c r="O84">
-        <v>-733.0676702000002</v>
+        <v>-744.2788613000001</v>
       </c>
       <c r="P84">
-        <v>-5131.473691400001</v>
+        <v>-5209.952029100001</v>
       </c>
       <c r="Q84">
-        <v>-4417.473691400001</v>
+        <v>-4495.952029100001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3119259726774529</v>
+        <v>0.3275804416584796</v>
       </c>
       <c r="T84">
-        <v>5.187290547496016</v>
+        <v>5.492425285584018</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.02532448875363736</v>
+        <v>0.02501937443130438</v>
       </c>
       <c r="W84">
-        <v>0.1957148426582696</v>
+        <v>0.1957761096141941</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2025959100290988</v>
+        <v>0.200154995450435</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2181828460617226</v>
+        <v>0.2492836289649542</v>
       </c>
       <c r="C85">
-        <v>-24263.95827286966</v>
+        <v>-26630.90777628859</v>
       </c>
       <c r="D85">
-        <v>12563.90472713035</v>
+        <v>10643.61622371141</v>
       </c>
       <c r="E85">
-        <v>31874.863</v>
+        <v>32321.524</v>
       </c>
       <c r="F85">
-        <v>37072.863</v>
+        <v>37519.524</v>
       </c>
       <c r="G85">
         <v>245</v>
@@ -8263,45 +8263,45 @@
         <v>1490</v>
       </c>
       <c r="M85">
-        <v>7444.230890400001</v>
+        <v>8847.103759200001</v>
       </c>
       <c r="N85">
-        <v>-5954.230890400001</v>
+        <v>-7357.103759200001</v>
       </c>
       <c r="O85">
-        <v>-744.2788613000001</v>
+        <v>-919.6379699000001</v>
       </c>
       <c r="P85">
-        <v>-5209.952029100001</v>
+        <v>-6437.465789300001</v>
       </c>
       <c r="Q85">
-        <v>-4495.952029100001</v>
+        <v>-5723.465789300001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3275804416584796</v>
+        <v>0.3461341124073319</v>
       </c>
       <c r="T85">
-        <v>5.492425285584018</v>
+        <v>5.854070862408353</v>
       </c>
       <c r="U85">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02501937443130438</v>
+        <v>0.02105208722191381</v>
       </c>
       <c r="W85">
-        <v>0.1957761096141941</v>
+        <v>0.2308359178330728</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.200154995450435</v>
+        <v>0.1684166977753105</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2492836289649542</v>
+        <v>0.2511836289649542</v>
       </c>
       <c r="C86">
-        <v>-26630.90777628858</v>
+        <v>-27176.03266519232</v>
       </c>
       <c r="D86">
-        <v>10643.61622371141</v>
+        <v>10545.15233480768</v>
       </c>
       <c r="E86">
-        <v>32321.524</v>
+        <v>32768.185</v>
       </c>
       <c r="F86">
-        <v>37519.524</v>
+        <v>37966.185</v>
       </c>
       <c r="G86">
         <v>245</v>
@@ -8345,37 +8345,37 @@
         <v>1490</v>
       </c>
       <c r="M86">
-        <v>8847.103759199999</v>
+        <v>8952.426422999999</v>
       </c>
       <c r="N86">
-        <v>-7357.103759199999</v>
+        <v>-7462.426422999999</v>
       </c>
       <c r="O86">
-        <v>-919.6379698999999</v>
+        <v>-932.8033028749999</v>
       </c>
       <c r="P86">
-        <v>-6437.465789299999</v>
+        <v>-6529.623120124999</v>
       </c>
       <c r="Q86">
-        <v>-5723.465789299999</v>
+        <v>-5815.623120124999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3461341124073317</v>
+        <v>0.3661563865678205</v>
       </c>
       <c r="T86">
-        <v>5.854070862408348</v>
+        <v>6.244342253235572</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02105208722191382</v>
+        <v>0.02080441560753836</v>
       </c>
       <c r="W86">
-        <v>0.2308359178330728</v>
+        <v>0.2308943187997425</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1684166977753105</v>
+        <v>0.1664353248603069</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2511836289649542</v>
+        <v>0.2530836289649541</v>
       </c>
       <c r="C87">
-        <v>-27176.03266519232</v>
+        <v>-27719.35247773907</v>
       </c>
       <c r="D87">
-        <v>10545.15233480768</v>
+        <v>10448.49352226092</v>
       </c>
       <c r="E87">
-        <v>32768.185</v>
+        <v>33214.846</v>
       </c>
       <c r="F87">
-        <v>37966.185</v>
+        <v>38412.846</v>
       </c>
       <c r="G87">
         <v>245</v>
@@ -8427,37 +8427,37 @@
         <v>1490</v>
       </c>
       <c r="M87">
-        <v>8952.426422999999</v>
+        <v>9057.7490868</v>
       </c>
       <c r="N87">
-        <v>-7462.426422999999</v>
+        <v>-7567.7490868</v>
       </c>
       <c r="O87">
-        <v>-932.8033028749999</v>
+        <v>-945.9686358500001</v>
       </c>
       <c r="P87">
-        <v>-6529.623120124999</v>
+        <v>-6621.78045095</v>
       </c>
       <c r="Q87">
-        <v>-5815.623120124999</v>
+        <v>-5907.78045095</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3661563865678205</v>
+        <v>0.389038985608379</v>
       </c>
       <c r="T87">
-        <v>6.244342253235572</v>
+        <v>6.690366699895256</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02080441560753836</v>
+        <v>0.02056250379814838</v>
       </c>
       <c r="W87">
-        <v>0.2308943187997425</v>
+        <v>0.2309513616043966</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1664353248603069</v>
+        <v>0.164500030385187</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2530836289649541</v>
+        <v>0.2549836289649542</v>
       </c>
       <c r="C88">
-        <v>-27719.35247773907</v>
+        <v>-28260.91640006873</v>
       </c>
       <c r="D88">
-        <v>10448.49352226092</v>
+        <v>10353.59059993127</v>
       </c>
       <c r="E88">
-        <v>33214.846</v>
+        <v>33661.507</v>
       </c>
       <c r="F88">
-        <v>38412.846</v>
+        <v>38859.507</v>
       </c>
       <c r="G88">
         <v>245</v>
@@ -8509,37 +8509,37 @@
         <v>1490</v>
       </c>
       <c r="M88">
-        <v>9057.7490868</v>
+        <v>9163.0717506</v>
       </c>
       <c r="N88">
-        <v>-7567.7490868</v>
+        <v>-7673.0717506</v>
       </c>
       <c r="O88">
-        <v>-945.9686358500001</v>
+        <v>-959.133968825</v>
       </c>
       <c r="P88">
-        <v>-6621.78045095</v>
+        <v>-6713.937781775</v>
       </c>
       <c r="Q88">
-        <v>-5907.78045095</v>
+        <v>-5999.937781775</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.389038985608379</v>
+        <v>0.4154419845013312</v>
       </c>
       <c r="T88">
-        <v>6.690366699895256</v>
+        <v>7.20501029219489</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02056250379814838</v>
+        <v>0.02032615317977885</v>
       </c>
       <c r="W88">
-        <v>0.2309513616043966</v>
+        <v>0.2310070930802082</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.164500030385187</v>
+        <v>0.1626092254382309</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2549836289649542</v>
+        <v>0.2568836289649541</v>
       </c>
       <c r="C89">
-        <v>-28260.91640006873</v>
+        <v>-28800.77184738958</v>
       </c>
       <c r="D89">
-        <v>10353.59059993127</v>
+        <v>10260.39615261041</v>
       </c>
       <c r="E89">
-        <v>33661.507</v>
+        <v>34108.168</v>
       </c>
       <c r="F89">
-        <v>38859.507</v>
+        <v>39306.168</v>
       </c>
       <c r="G89">
         <v>245</v>
@@ -8591,37 +8591,37 @@
         <v>1490</v>
       </c>
       <c r="M89">
-        <v>9163.0717506</v>
+        <v>9268.3944144</v>
       </c>
       <c r="N89">
-        <v>-7673.0717506</v>
+        <v>-7778.3944144</v>
       </c>
       <c r="O89">
-        <v>-959.133968825</v>
+        <v>-972.2993018</v>
       </c>
       <c r="P89">
-        <v>-6713.937781775</v>
+        <v>-6806.0951126</v>
       </c>
       <c r="Q89">
-        <v>-5999.937781775</v>
+        <v>-6092.0951126</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4154419845013312</v>
+        <v>0.4462454832097755</v>
       </c>
       <c r="T89">
-        <v>7.20501029219489</v>
+        <v>7.805427816544465</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02032615317977885</v>
+        <v>0.02009517416637228</v>
       </c>
       <c r="W89">
-        <v>0.2310070930802082</v>
+        <v>0.2310615579315694</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1626092254382309</v>
+        <v>0.1607613933309783</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2568836289649541</v>
+        <v>0.2587836289649542</v>
       </c>
       <c r="C90">
-        <v>-28800.77184738958</v>
+        <v>-29338.96454296966</v>
       </c>
       <c r="D90">
-        <v>10260.39615261041</v>
+        <v>10168.86445703034</v>
       </c>
       <c r="E90">
-        <v>34108.168</v>
+        <v>34554.829</v>
       </c>
       <c r="F90">
-        <v>39306.168</v>
+        <v>39752.829</v>
       </c>
       <c r="G90">
         <v>245</v>
@@ -8673,37 +8673,37 @@
         <v>1490</v>
       </c>
       <c r="M90">
-        <v>9268.3944144</v>
+        <v>9373.717078199999</v>
       </c>
       <c r="N90">
-        <v>-7778.3944144</v>
+        <v>-7883.717078199999</v>
       </c>
       <c r="O90">
-        <v>-972.2993018</v>
+        <v>-985.4646347749999</v>
       </c>
       <c r="P90">
-        <v>-6806.0951126</v>
+        <v>-6898.252443424999</v>
       </c>
       <c r="Q90">
-        <v>-6092.0951126</v>
+        <v>-6184.252443424999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4462454832097755</v>
+        <v>0.482649618047028</v>
       </c>
       <c r="T90">
-        <v>7.805427816544465</v>
+        <v>8.515012163503055</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02009517416637228</v>
+        <v>0.01986938569259282</v>
       </c>
       <c r="W90">
-        <v>0.2310615579315694</v>
+        <v>0.2311147988536866</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1607613933309783</v>
+        <v>0.1589550855407426</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2587836289649542</v>
+        <v>0.2606836289649542</v>
       </c>
       <c r="C91">
-        <v>-29338.96454296966</v>
+        <v>-29875.53859293732</v>
       </c>
       <c r="D91">
-        <v>10168.86445703034</v>
+        <v>10078.95140706268</v>
       </c>
       <c r="E91">
-        <v>34554.829</v>
+        <v>35001.49</v>
       </c>
       <c r="F91">
-        <v>39752.829</v>
+        <v>40199.49</v>
       </c>
       <c r="G91">
         <v>245</v>
@@ -8755,37 +8755,37 @@
         <v>1490</v>
       </c>
       <c r="M91">
-        <v>9373.717078199999</v>
+        <v>9479.039741999999</v>
       </c>
       <c r="N91">
-        <v>-7883.717078199999</v>
+        <v>-7989.039741999999</v>
       </c>
       <c r="O91">
-        <v>-985.4646347749999</v>
+        <v>-998.6299677499999</v>
       </c>
       <c r="P91">
-        <v>-6898.252443424999</v>
+        <v>-6990.409774249999</v>
       </c>
       <c r="Q91">
-        <v>-6184.252443424999</v>
+        <v>-6276.409774249999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.482649618047028</v>
+        <v>0.5263345798517308</v>
       </c>
       <c r="T91">
-        <v>8.515012163503055</v>
+        <v>9.366513379853361</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01986938569259282</v>
+        <v>0.0196486147404529</v>
       </c>
       <c r="W91">
-        <v>0.2311147988536866</v>
+        <v>0.2311668566442012</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1589550855407426</v>
+        <v>0.1571889179236232</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2606836289649542</v>
+        <v>0.2625836289649541</v>
       </c>
       <c r="C92">
-        <v>-29875.53859293732</v>
+        <v>-30410.53655714836</v>
       </c>
       <c r="D92">
-        <v>10078.95140706268</v>
+        <v>9990.614442851633</v>
       </c>
       <c r="E92">
-        <v>35001.49</v>
+        <v>35448.151</v>
       </c>
       <c r="F92">
-        <v>40199.49</v>
+        <v>40646.151</v>
       </c>
       <c r="G92">
         <v>245</v>
@@ -8837,37 +8837,37 @@
         <v>1490</v>
       </c>
       <c r="M92">
-        <v>9479.039741999999</v>
+        <v>9584.3624058</v>
       </c>
       <c r="N92">
-        <v>-7989.039741999999</v>
+        <v>-8094.3624058</v>
       </c>
       <c r="O92">
-        <v>-998.6299677499999</v>
+        <v>-1011.795300725</v>
       </c>
       <c r="P92">
-        <v>-6990.409774249999</v>
+        <v>-7082.567105075001</v>
       </c>
       <c r="Q92">
-        <v>-6276.409774249999</v>
+        <v>-6368.567105075001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5263345798517308</v>
+        <v>0.5797273109463675</v>
       </c>
       <c r="T92">
-        <v>9.366513379853361</v>
+        <v>10.40723708872596</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0196486147404529</v>
+        <v>0.01943269589715121</v>
       </c>
       <c r="W92">
-        <v>0.2311668566442012</v>
+        <v>0.2312177703074517</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1571889179236232</v>
+        <v>0.1554615671772097</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2625836289649541</v>
+        <v>0.2644836289649541</v>
       </c>
       <c r="C93">
-        <v>-30410.53655714836</v>
+        <v>-30943.99951635886</v>
       </c>
       <c r="D93">
-        <v>9990.614442851633</v>
+        <v>9903.812483641141</v>
       </c>
       <c r="E93">
-        <v>35448.151</v>
+        <v>35894.812</v>
       </c>
       <c r="F93">
-        <v>40646.151</v>
+        <v>41092.812</v>
       </c>
       <c r="G93">
         <v>245</v>
@@ -8919,37 +8919,37 @@
         <v>1490</v>
       </c>
       <c r="M93">
-        <v>9584.3624058</v>
+        <v>9689.6850696</v>
       </c>
       <c r="N93">
-        <v>-8094.3624058</v>
+        <v>-8199.6850696</v>
       </c>
       <c r="O93">
-        <v>-1011.795300725</v>
+        <v>-1024.9606337</v>
       </c>
       <c r="P93">
-        <v>-7082.567105075001</v>
+        <v>-7174.7244359</v>
       </c>
       <c r="Q93">
-        <v>-6368.567105075001</v>
+        <v>-6460.7244359</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5797273109463675</v>
+        <v>0.6464682248146636</v>
       </c>
       <c r="T93">
-        <v>10.40723708872596</v>
+        <v>11.7081417248167</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01943269589715121</v>
+        <v>0.0192214709417474</v>
       </c>
       <c r="W93">
-        <v>0.2312177703074517</v>
+        <v>0.231267577151936</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1554615671772097</v>
+        <v>0.1537717675339791</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2644836289649541</v>
+        <v>0.2663836289649542</v>
       </c>
       <c r="C94">
-        <v>-30943.99951635886</v>
+        <v>-31475.9671359263</v>
       </c>
       <c r="D94">
-        <v>9903.812483641141</v>
+        <v>9818.505864073699</v>
       </c>
       <c r="E94">
-        <v>35894.812</v>
+        <v>36341.473</v>
       </c>
       <c r="F94">
-        <v>41092.812</v>
+        <v>41539.473</v>
       </c>
       <c r="G94">
         <v>245</v>
@@ -9001,37 +9001,37 @@
         <v>1490</v>
       </c>
       <c r="M94">
-        <v>9689.6850696</v>
+        <v>9795.0077334</v>
       </c>
       <c r="N94">
-        <v>-8199.6850696</v>
+        <v>-8305.0077334</v>
       </c>
       <c r="O94">
-        <v>-1024.9606337</v>
+        <v>-1038.125966675</v>
       </c>
       <c r="P94">
-        <v>-7174.7244359</v>
+        <v>-7266.881766725</v>
       </c>
       <c r="Q94">
-        <v>-6460.7244359</v>
+        <v>-6552.881766725</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6464682248146636</v>
+        <v>0.7322779712167585</v>
       </c>
       <c r="T94">
-        <v>11.7081417248167</v>
+        <v>13.38073339979052</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0192214709417474</v>
+        <v>0.0190147884585028</v>
       </c>
       <c r="W94">
-        <v>0.231267577151936</v>
+        <v>0.231316312881485</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1537717675339791</v>
+        <v>0.1521183076680224</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2663836289649542</v>
+        <v>0.2682836289649542</v>
       </c>
       <c r="C95">
-        <v>-31475.9671359263</v>
+        <v>-32006.47772624685</v>
       </c>
       <c r="D95">
-        <v>9818.505864073699</v>
+        <v>9734.656273753153</v>
       </c>
       <c r="E95">
-        <v>36341.473</v>
+        <v>36788.134</v>
       </c>
       <c r="F95">
-        <v>41539.473</v>
+        <v>41986.134</v>
       </c>
       <c r="G95">
         <v>245</v>
@@ -9083,37 +9083,37 @@
         <v>1490</v>
       </c>
       <c r="M95">
-        <v>9795.0077334</v>
+        <v>9900.330397199999</v>
       </c>
       <c r="N95">
-        <v>-8305.0077334</v>
+        <v>-8410.330397199999</v>
       </c>
       <c r="O95">
-        <v>-1038.125966675</v>
+        <v>-1051.29129965</v>
       </c>
       <c r="P95">
-        <v>-7266.881766725</v>
+        <v>-7359.039097549999</v>
       </c>
       <c r="Q95">
-        <v>-6552.881766725</v>
+        <v>-6645.039097549999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7322779712167585</v>
+        <v>0.8466909664195518</v>
       </c>
       <c r="T95">
-        <v>13.38073339979052</v>
+        <v>15.61085563308894</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.0190147884585028</v>
+        <v>0.01881250347490171</v>
       </c>
       <c r="W95">
-        <v>0.231316312881485</v>
+        <v>0.2313640116806182</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1521183076680224</v>
+        <v>0.1505000277992137</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2682836289649542</v>
+        <v>0.2701836289649542</v>
       </c>
       <c r="C96">
-        <v>-32006.47772624685</v>
+        <v>-32535.56830012195</v>
       </c>
       <c r="D96">
-        <v>9734.656273753153</v>
+        <v>9652.226699878047</v>
       </c>
       <c r="E96">
-        <v>36788.134</v>
+        <v>37234.795</v>
       </c>
       <c r="F96">
-        <v>41986.134</v>
+        <v>42432.795</v>
       </c>
       <c r="G96">
         <v>245</v>
@@ -9165,37 +9165,37 @@
         <v>1490</v>
       </c>
       <c r="M96">
-        <v>9900.330397199999</v>
+        <v>10005.653061</v>
       </c>
       <c r="N96">
-        <v>-8410.330397199999</v>
+        <v>-8515.653061000001</v>
       </c>
       <c r="O96">
-        <v>-1051.29129965</v>
+        <v>-1064.456632625</v>
       </c>
       <c r="P96">
-        <v>-7359.039097549999</v>
+        <v>-7451.196428375</v>
       </c>
       <c r="Q96">
-        <v>-6645.039097549999</v>
+        <v>-6737.196428375</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8466909664195518</v>
+        <v>1.006869159703463</v>
       </c>
       <c r="T96">
-        <v>15.61085563308894</v>
+        <v>18.73302675970675</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01881250347490171</v>
+        <v>0.01861447712253432</v>
       </c>
       <c r="W96">
-        <v>0.2313640116806182</v>
+        <v>0.2314107062945064</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1505000277992137</v>
+        <v>0.1489158169802746</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2701836289649542</v>
+        <v>0.2720836289649541</v>
       </c>
       <c r="C97">
-        <v>-32535.56830012195</v>
+        <v>-33063.2746272349</v>
       </c>
       <c r="D97">
-        <v>9652.226699878047</v>
+        <v>9571.181372765108</v>
       </c>
       <c r="E97">
-        <v>37234.795</v>
+        <v>37681.45600000001</v>
       </c>
       <c r="F97">
-        <v>42432.795</v>
+        <v>42879.45600000001</v>
       </c>
       <c r="G97">
         <v>245</v>
@@ -9247,37 +9247,37 @@
         <v>1490</v>
       </c>
       <c r="M97">
-        <v>10005.653061</v>
+        <v>10110.9757248</v>
       </c>
       <c r="N97">
-        <v>-8515.653061000001</v>
+        <v>-8620.975724800002</v>
       </c>
       <c r="O97">
-        <v>-1064.456632625</v>
+        <v>-1077.6219656</v>
       </c>
       <c r="P97">
-        <v>-7451.196428375</v>
+        <v>-7543.353759200002</v>
       </c>
       <c r="Q97">
-        <v>-6737.196428375</v>
+        <v>-6829.353759200002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.006869159703463</v>
+        <v>1.247136449629329</v>
       </c>
       <c r="T97">
-        <v>18.73302675970675</v>
+        <v>23.41628344963344</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01861447712253432</v>
+        <v>0.01842057631917458</v>
       </c>
       <c r="W97">
-        <v>0.2314107062945064</v>
+        <v>0.2314564281039386</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1489158169802746</v>
+        <v>0.1473646105533967</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2720836289649541</v>
+        <v>0.2739836289649542</v>
       </c>
       <c r="C98">
-        <v>-33063.27462723489</v>
+        <v>-33589.63128590569</v>
       </c>
       <c r="D98">
-        <v>9571.181372765108</v>
+        <v>9491.485714094315</v>
       </c>
       <c r="E98">
-        <v>37681.456</v>
+        <v>38128.117</v>
       </c>
       <c r="F98">
-        <v>42879.456</v>
+        <v>43326.117</v>
       </c>
       <c r="G98">
         <v>245</v>
@@ -9329,37 +9329,37 @@
         <v>1490</v>
       </c>
       <c r="M98">
-        <v>10110.9757248</v>
+        <v>10216.2983886</v>
       </c>
       <c r="N98">
-        <v>-8620.975724800001</v>
+        <v>-8726.2983886</v>
       </c>
       <c r="O98">
-        <v>-1077.6219656</v>
+        <v>-1090.787298575</v>
       </c>
       <c r="P98">
-        <v>-7543.3537592</v>
+        <v>-7635.511090025</v>
       </c>
       <c r="Q98">
-        <v>-6829.3537592</v>
+        <v>-6921.511090025</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.247136449629326</v>
+        <v>1.647581932839101</v>
       </c>
       <c r="T98">
-        <v>23.41628344963338</v>
+        <v>31.22171126617783</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01842057631917459</v>
+        <v>0.0182306734705233</v>
       </c>
       <c r="W98">
-        <v>0.2314564281039386</v>
+        <v>0.2315012071956506</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1473646105533967</v>
+        <v>0.1458453877641864</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2739836289649542</v>
+        <v>0.2758836289649542</v>
       </c>
       <c r="C99">
-        <v>-33589.63128590569</v>
+        <v>-34114.67171228168</v>
       </c>
       <c r="D99">
-        <v>9491.485714094315</v>
+        <v>9413.106287718323</v>
       </c>
       <c r="E99">
-        <v>38128.117</v>
+        <v>38574.778</v>
       </c>
       <c r="F99">
-        <v>43326.117</v>
+        <v>43772.778</v>
       </c>
       <c r="G99">
         <v>245</v>
@@ -9411,37 +9411,37 @@
         <v>1490</v>
       </c>
       <c r="M99">
-        <v>10216.2983886</v>
+        <v>10321.6210524</v>
       </c>
       <c r="N99">
-        <v>-8726.2983886</v>
+        <v>-8831.6210524</v>
       </c>
       <c r="O99">
-        <v>-1090.787298575</v>
+        <v>-1103.95263155</v>
       </c>
       <c r="P99">
-        <v>-7635.511090025</v>
+        <v>-7727.66842085</v>
       </c>
       <c r="Q99">
-        <v>-6921.511090025</v>
+        <v>-7013.66842085</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.647581932839101</v>
+        <v>2.448472899258651</v>
       </c>
       <c r="T99">
-        <v>31.22171126617783</v>
+        <v>46.83256689926675</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0182306734705233</v>
+        <v>0.01804464619021184</v>
       </c>
       <c r="W99">
-        <v>0.2315012071956506</v>
+        <v>0.2315450724283481</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1458453877641864</v>
+        <v>0.1443571695216948</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2758836289649542</v>
+        <v>0.2777836289649541</v>
       </c>
       <c r="C100">
-        <v>-34114.67171228168</v>
+        <v>-34638.42824711085</v>
       </c>
       <c r="D100">
-        <v>9413.106287718323</v>
+        <v>9336.010752889155</v>
       </c>
       <c r="E100">
-        <v>38574.778</v>
+        <v>39021.439</v>
       </c>
       <c r="F100">
-        <v>43772.778</v>
+        <v>44219.439</v>
       </c>
       <c r="G100">
         <v>245</v>
@@ -9493,37 +9493,37 @@
         <v>1490</v>
       </c>
       <c r="M100">
-        <v>10321.6210524</v>
+        <v>10426.9437162</v>
       </c>
       <c r="N100">
-        <v>-8831.6210524</v>
+        <v>-8936.943716199999</v>
       </c>
       <c r="O100">
-        <v>-1103.95263155</v>
+        <v>-1117.117964525</v>
       </c>
       <c r="P100">
-        <v>-7727.66842085</v>
+        <v>-7819.825751675</v>
       </c>
       <c r="Q100">
-        <v>-7013.66842085</v>
+        <v>-7105.825751675</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.448472899258651</v>
+        <v>4.851145798517303</v>
       </c>
       <c r="T100">
-        <v>46.83256689926675</v>
+        <v>93.6651337985335</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01804464619021184</v>
+        <v>0.01786237703677536</v>
       </c>
       <c r="W100">
-        <v>0.2315450724283481</v>
+        <v>0.2315880514947284</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1443571695216948</v>
+        <v>0.1428990162942029</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2777836289649541</v>
-      </c>
-      <c r="C101">
-        <v>-34638.42824711085</v>
-      </c>
-      <c r="D101">
-        <v>9336.010752889155</v>
-      </c>
-      <c r="E101">
-        <v>39021.439</v>
-      </c>
-      <c r="F101">
-        <v>44219.439</v>
-      </c>
-      <c r="G101">
-        <v>245</v>
-      </c>
-      <c r="H101">
-        <v>39468.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2204</v>
-      </c>
-      <c r="K101">
-        <v>714</v>
-      </c>
-      <c r="L101">
-        <v>1490</v>
-      </c>
-      <c r="M101">
-        <v>10426.9437162</v>
-      </c>
-      <c r="N101">
-        <v>-8936.943716199999</v>
-      </c>
-      <c r="O101">
-        <v>-1117.117964525</v>
-      </c>
-      <c r="P101">
-        <v>-7819.825751675</v>
-      </c>
-      <c r="Q101">
-        <v>-7105.825751675</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.851145798517303</v>
-      </c>
-      <c r="T101">
-        <v>93.6651337985335</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01786237703677536</v>
-      </c>
-      <c r="W101">
-        <v>0.2315880514947284</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1428990162942029</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
